--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>59453</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>13.9700002670288</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>13.6099996566772</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>13.7200002670288</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>94938</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>13.8599996566772</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>13.539999961853</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>13.7600002288818</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>13.6599998474121</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>36595</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>13.8599996566772</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>13.6000003814697</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>13.6000003814697</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>64802</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>14.0200004577637</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>13.7299995422363</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>13.7299995422363</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>13.8299999237061</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>107824</v>
+        <v>35851</v>
       </c>
       <c r="C2715" t="n">
+        <v>14.6800003051758</v>
+      </c>
+      <c r="D2715" t="n">
         <v>14.4700002670288</v>
       </c>
-      <c r="D2715" t="n">
-        <v>14.1599998474121</v>
-      </c>
       <c r="E2715" t="n">
-        <v>14.3999996185303</v>
+        <v>14.6800003051758</v>
       </c>
       <c r="F2715" t="n">
-        <v>14.3900003433228</v>
+        <v>14.5799999237061</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>117762</v>
+        <v>107824</v>
       </c>
       <c r="C2716" t="n">
-        <v>14.3500003814697</v>
+        <v>14.4700002670288</v>
       </c>
       <c r="D2716" t="n">
-        <v>13.8699998855591</v>
+        <v>14.1599998474121</v>
       </c>
       <c r="E2716" t="n">
-        <v>14.2600002288818</v>
+        <v>14.3999996185303</v>
       </c>
       <c r="F2716" t="n">
-        <v>13.9700002670288</v>
+        <v>14.3900003433228</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>978307</v>
+        <v>117762</v>
       </c>
       <c r="C2717" t="n">
-        <v>14.1400003433228</v>
+        <v>14.3500003814697</v>
       </c>
       <c r="D2717" t="n">
-        <v>13.7700004577637</v>
+        <v>13.8699998855591</v>
       </c>
       <c r="E2717" t="n">
+        <v>14.2600002288818</v>
+      </c>
+      <c r="F2717" t="n">
         <v>13.9700002670288</v>
-      </c>
-      <c r="F2717" t="n">
-        <v>13.7700004577637</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>82252</v>
+        <v>978307</v>
       </c>
       <c r="C2718" t="n">
-        <v>13.9799995422363</v>
+        <v>14.1400003433228</v>
       </c>
       <c r="D2718" t="n">
-        <v>13.7399997711182</v>
+        <v>13.7700004577637</v>
       </c>
       <c r="E2718" t="n">
-        <v>13.8999996185303</v>
+        <v>13.9700002670288</v>
       </c>
       <c r="F2718" t="n">
-        <v>13.7600002288818</v>
+        <v>13.7700004577637</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>59453</v>
+        <v>82252</v>
       </c>
       <c r="C2719" t="n">
-        <v>13.9700002670288</v>
+        <v>13.9799995422363</v>
       </c>
       <c r="D2719" t="n">
-        <v>13.6099996566772</v>
+        <v>13.7399997711182</v>
       </c>
       <c r="E2719" t="n">
-        <v>13.6999998092651</v>
+        <v>13.8999996185303</v>
       </c>
       <c r="F2719" t="n">
-        <v>13.7200002670288</v>
+        <v>13.7600002288818</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>94938</v>
+        <v>59453</v>
       </c>
       <c r="C2720" t="n">
-        <v>13.8599996566772</v>
+        <v>13.9700002670288</v>
       </c>
       <c r="D2720" t="n">
-        <v>13.539999961853</v>
+        <v>13.6099996566772</v>
       </c>
       <c r="E2720" t="n">
-        <v>13.7600002288818</v>
+        <v>13.6999998092651</v>
       </c>
       <c r="F2720" t="n">
-        <v>13.6599998474121</v>
+        <v>13.7200002670288</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>36595</v>
+        <v>94938</v>
       </c>
       <c r="C2721" t="n">
         <v>13.8599996566772</v>
       </c>
       <c r="D2721" t="n">
-        <v>13.6000003814697</v>
+        <v>13.539999961853</v>
       </c>
       <c r="E2721" t="n">
-        <v>13.6000003814697</v>
+        <v>13.7600002288818</v>
       </c>
       <c r="F2721" t="n">
-        <v>13.8000001907349</v>
+        <v>13.6599998474121</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>64802</v>
+        <v>36595</v>
       </c>
       <c r="C2722" t="n">
-        <v>14.0200004577637</v>
+        <v>13.8599996566772</v>
       </c>
       <c r="D2722" t="n">
-        <v>13.7299995422363</v>
+        <v>13.6000003814697</v>
       </c>
       <c r="E2722" t="n">
-        <v>13.7299995422363</v>
+        <v>13.6000003814697</v>
       </c>
       <c r="F2722" t="n">
-        <v>13.8299999237061</v>
+        <v>13.8000001907349</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>64428</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>13.9099998474121</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>13.6599998474121</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>13.6199998855591</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>13.3000001907349</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>13.1599998474121</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>37220</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>13.4099998474121</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>13.2399997711182</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>13.25</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>13.3699998855591</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>46155</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>13.3800001144409</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>13.0299997329712</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -63311,13 +63311,36 @@
         <v>13.3800001144409</v>
       </c>
       <c r="D2737" t="n">
-        <v>13.0299997329712</v>
+        <v>13.0100002288818</v>
       </c>
       <c r="E2737" t="n">
         <v>13.25</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>13.0100002288818</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>59159</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>13.0900001525879</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>12.710000038147</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>13</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>12.9499998092651</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>33679</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>13.3199996948242</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>13.0699996948242</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>13.1199998855591</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>281260</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>13.1999998092651</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>12.8800001144409</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>12.5200004577637</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G2" t="n">
-        <v>4.60500383377075</v>
+        <v>4.60500431060791</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G3" t="n">
-        <v>4.58154916763306</v>
+        <v>4.58154821395874</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G4" t="n">
-        <v>4.46036529541016</v>
+        <v>4.460364818573</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>4.39390850067139</v>
+        <v>4.39390802383423</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>4.23363208770752</v>
+        <v>4.23363256454468</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.375</v>
       </c>
       <c r="G10" t="n">
-        <v>4.20235824584961</v>
+        <v>4.20235967636108</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>3.97562718391418</v>
+        <v>3.97562742233276</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.92799997329712</v>
       </c>
       <c r="G12" t="n">
-        <v>3.85287928581238</v>
+        <v>3.85287880897522</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G15" t="n">
-        <v>3.75436878204346</v>
+        <v>3.7543683052063</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.94399976730347</v>
       </c>
       <c r="G16" t="n">
-        <v>3.86538863182068</v>
+        <v>3.86538910865784</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G17" t="n">
-        <v>3.79815053939819</v>
+        <v>3.79815101623535</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G18" t="n">
-        <v>3.83411526679993</v>
+        <v>3.83411622047424</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G19" t="n">
-        <v>3.79658699035645</v>
+        <v>3.7965874671936</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G20" t="n">
-        <v>3.66680240631104</v>
+        <v>3.66680216789246</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G21" t="n">
-        <v>3.85131597518921</v>
+        <v>3.85131573677063</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>3.79189610481262</v>
+        <v>3.7918963432312</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G23" t="n">
-        <v>3.65898418426514</v>
+        <v>3.65898466110229</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>3.50261735916138</v>
+        <v>3.50261807441711</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G26" t="n">
-        <v>3.54327344894409</v>
+        <v>3.54327321052551</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G27" t="n">
-        <v>3.2805769443512</v>
+        <v>3.28057670593262</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G28" t="n">
-        <v>3.08355450630188</v>
+        <v>3.0835542678833</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G29" t="n">
-        <v>3.18206572532654</v>
+        <v>3.18206548690796</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G30" t="n">
-        <v>3.06479024887085</v>
+        <v>3.06479072570801</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G32" t="n">
-        <v>3.36970567703247</v>
+        <v>3.36970591545105</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>3.29152250289917</v>
+        <v>3.29152226448059</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G35" t="n">
-        <v>3.47916221618652</v>
+        <v>3.4791624546051</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G36" t="n">
-        <v>3.27588582038879</v>
+        <v>3.27588558197021</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G37" t="n">
-        <v>3.31966781616211</v>
+        <v>3.31966829299927</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G38" t="n">
-        <v>3.29621338844299</v>
+        <v>3.29621362686157</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G39" t="n">
-        <v>3.17111992835999</v>
+        <v>3.17111968994141</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G40" t="n">
-        <v>3.22272133827209</v>
+        <v>3.22272109985352</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G42" t="n">
-        <v>3.36970567703247</v>
+        <v>3.36970591545105</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G44" t="n">
-        <v>3.55734610557556</v>
+        <v>3.55734586715698</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G46" t="n">
-        <v>3.56672763824463</v>
+        <v>3.56672835350037</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G47" t="n">
-        <v>3.48541712760925</v>
+        <v>3.48541784286499</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G48" t="n">
-        <v>3.44632577896118</v>
+        <v>3.44632530212402</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>3.42443442344666</v>
+        <v>3.42443418502808</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.41400003433228</v>
       </c>
       <c r="G50" t="n">
-        <v>3.45101642608643</v>
+        <v>3.451016664505</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.44399976730347</v>
       </c>
       <c r="G51" t="n">
-        <v>3.47447156906128</v>
+        <v>3.47447109222412</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G52" t="n">
-        <v>3.6730580329895</v>
+        <v>3.67305755615234</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G53" t="n">
-        <v>3.65898418426514</v>
+        <v>3.65898466110229</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G54" t="n">
-        <v>3.53701853752136</v>
+        <v>3.53701829910278</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G55" t="n">
-        <v>3.67462062835693</v>
+        <v>3.67462110519409</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G56" t="n">
-        <v>3.75124096870422</v>
+        <v>3.75124049186707</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>3.79189610481262</v>
+        <v>3.7918963432312</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G58" t="n">
-        <v>3.59331011772156</v>
+        <v>3.59331035614014</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G59" t="n">
-        <v>3.62927508354187</v>
+        <v>3.62927484512329</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G60" t="n">
-        <v>3.58080101013184</v>
+        <v>3.58080124855042</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.40399980545044</v>
       </c>
       <c r="G61" t="n">
-        <v>3.44319796562195</v>
+        <v>3.44319748878479</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G62" t="n">
-        <v>3.4947988986969</v>
+        <v>3.49479866027832</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G63" t="n">
-        <v>3.43537998199463</v>
+        <v>3.43537974357605</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G64" t="n">
-        <v>3.46821641921997</v>
+        <v>3.46821689605713</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G65" t="n">
-        <v>3.50418066978455</v>
+        <v>3.50418138504028</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G67" t="n">
-        <v>3.3384325504303</v>
+        <v>3.33843231201172</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G68" t="n">
-        <v>3.30403137207031</v>
+        <v>3.30403161048889</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G69" t="n">
-        <v>3.5245087146759</v>
+        <v>3.52450895309448</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G70" t="n">
-        <v>3.53701853752136</v>
+        <v>3.53701829910278</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G71" t="n">
-        <v>3.41192507743835</v>
+        <v>3.4119246006012</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G72" t="n">
-        <v>3.46978116035461</v>
+        <v>3.46978092193604</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G73" t="n">
-        <v>3.5198175907135</v>
+        <v>3.51981782913208</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G74" t="n">
-        <v>3.55734610557556</v>
+        <v>3.55734586715698</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G75" t="n">
-        <v>3.5198175907135</v>
+        <v>3.51981782913208</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G76" t="n">
-        <v>3.69964027404785</v>
+        <v>3.69963932037354</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G77" t="n">
-        <v>3.66523885726929</v>
+        <v>3.66523957252502</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.7762598991394</v>
+        <v>3.77625942230225</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G79" t="n">
-        <v>3.66054797172546</v>
+        <v>3.66054844856262</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G81" t="n">
-        <v>3.62771105766296</v>
+        <v>3.62771129608154</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G82" t="n">
-        <v>3.61520171165466</v>
+        <v>3.61520147323608</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G83" t="n">
-        <v>3.66680240631104</v>
+        <v>3.66680216789246</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G84" t="n">
-        <v>3.59956502914429</v>
+        <v>3.59956479072571</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G85" t="n">
-        <v>3.71684074401855</v>
+        <v>3.7168402671814</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G86" t="n">
-        <v>3.58861947059631</v>
+        <v>3.58861923217773</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G87" t="n">
-        <v>3.59331011772156</v>
+        <v>3.59331035614014</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.63399982452393</v>
       </c>
       <c r="G88" t="n">
-        <v>3.62301993370056</v>
+        <v>3.62302017211914</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>3.54952836036682</v>
+        <v>3.54952764511108</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G90" t="n">
-        <v>3.59643745422363</v>
+        <v>3.59643793106079</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G93" t="n">
-        <v>3.55734610557556</v>
+        <v>3.55734586715698</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>3.54952836036682</v>
+        <v>3.54952764511108</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>3.54952836036682</v>
+        <v>3.54952764511108</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G96" t="n">
-        <v>3.45570778846741</v>
+        <v>3.45570755004883</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>3.38534188270569</v>
+        <v>3.38534235954285</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G98" t="n">
-        <v>3.40097856521606</v>
+        <v>3.40097951889038</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>3.38534188270569</v>
+        <v>3.38534235954285</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G102" t="n">
-        <v>3.67825889587402</v>
+        <v>3.67825865745544</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G104" t="n">
-        <v>3.7935037612915</v>
+        <v>3.79350423812866</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.75</v>
       </c>
       <c r="G105" t="n">
-        <v>3.80150723457336</v>
+        <v>3.80150747299194</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G106" t="n">
-        <v>3.69746589660645</v>
+        <v>3.6974663734436</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G108" t="n">
-        <v>3.62703800201416</v>
+        <v>3.6270387172699</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G109" t="n">
-        <v>3.59182405471802</v>
+        <v>3.5918242931366</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G111" t="n">
-        <v>3.50859117507935</v>
+        <v>3.5085916519165</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G112" t="n">
-        <v>3.48138046264648</v>
+        <v>3.48138093948364</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G113" t="n">
-        <v>3.31491494178772</v>
+        <v>3.31491446495056</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G115" t="n">
-        <v>3.22848010063171</v>
+        <v>3.22848033905029</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G118" t="n">
-        <v>3.09242606163025</v>
+        <v>3.09242630004883</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G120" t="n">
-        <v>3.08762454986572</v>
+        <v>3.08762431144714</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G121" t="n">
-        <v>2.97077798843384</v>
+        <v>2.97077751159668</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G122" t="n">
-        <v>3.15485119819641</v>
+        <v>3.15485095977783</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G123" t="n">
-        <v>3.28130102157593</v>
+        <v>3.28130125999451</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G124" t="n">
-        <v>3.0412061214447</v>
+        <v>3.04120588302612</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>2.76909828186035</v>
+        <v>2.76909804344177</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G126" t="n">
-        <v>2.76109528541565</v>
+        <v>2.76109504699707</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G128" t="n">
-        <v>2.87313961982727</v>
+        <v>2.87313938140869</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G129" t="n">
-        <v>2.97878170013428</v>
+        <v>2.97878098487854</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G130" t="n">
-        <v>2.89554858207703</v>
+        <v>2.89554810523987</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G132" t="n">
-        <v>2.70507287979126</v>
+        <v>2.70507311820984</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G134" t="n">
-        <v>2.78830552101135</v>
+        <v>2.78830599784851</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>2.81711745262146</v>
+        <v>2.8171169757843</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.83200001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>3.06681609153748</v>
+        <v>3.06681656837463</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G143" t="n">
-        <v>2.91315531730652</v>
+        <v>2.91315507888794</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G146" t="n">
-        <v>3.10843324661255</v>
+        <v>3.10843276977539</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G148" t="n">
-        <v>3.08922481536865</v>
+        <v>3.08922505378723</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>3.03320288658142</v>
+        <v>3.03320264816284</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G153" t="n">
-        <v>2.96117472648621</v>
+        <v>2.96117448806763</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G155" t="n">
-        <v>3.16925716400146</v>
+        <v>3.16925668716431</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G156" t="n">
-        <v>3.2108736038208</v>
+        <v>3.21087336540222</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>3.16925716400146</v>
+        <v>3.16925668716431</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G158" t="n">
-        <v>3.25248980522156</v>
+        <v>3.25249004364014</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>3.28130102157593</v>
+        <v>3.28130125999451</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G161" t="n">
-        <v>3.33412218093872</v>
+        <v>3.33412265777588</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G163" t="n">
-        <v>3.36453461647034</v>
+        <v>3.36453413963318</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>3.48138046264648</v>
+        <v>3.48138093948364</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G169" t="n">
-        <v>3.56941556930542</v>
+        <v>3.56941533088684</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G173" t="n">
-        <v>3.77109551429749</v>
+        <v>3.77109527587891</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G174" t="n">
-        <v>3.72787809371948</v>
+        <v>3.72787833213806</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>4.67600011825562</v>
       </c>
       <c r="G175" t="n">
-        <v>3.74228477478027</v>
+        <v>3.74228405952454</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.67600011825562</v>
       </c>
       <c r="G176" t="n">
-        <v>3.74228477478027</v>
+        <v>3.74228405952454</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G178" t="n">
-        <v>3.66385364532471</v>
+        <v>3.66385316848755</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G179" t="n">
-        <v>3.54700660705566</v>
+        <v>3.54700708389282</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.25</v>
       </c>
       <c r="G181" t="n">
-        <v>3.40134859085083</v>
+        <v>3.40134906768799</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>3.44136500358582</v>
+        <v>3.44136476516724</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.47599983215332</v>
       </c>
       <c r="G184" t="n">
-        <v>3.58222031593323</v>
+        <v>3.58222055435181</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>3.52939963340759</v>
+        <v>3.52940011024475</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G187" t="n">
-        <v>3.57101631164551</v>
+        <v>3.57101678848267</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G188" t="n">
-        <v>3.56781530380249</v>
+        <v>3.56781554222107</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>3.44136500358582</v>
+        <v>3.44136476516724</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G191" t="n">
-        <v>3.40935182571411</v>
+        <v>3.40935230255127</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G193" t="n">
-        <v>3.361332654953</v>
+        <v>3.36133289337158</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.25</v>
       </c>
       <c r="G195" t="n">
-        <v>3.40134859085083</v>
+        <v>3.40134906768799</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G196" t="n">
-        <v>3.48138046264648</v>
+        <v>3.48138093948364</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G200" t="n">
-        <v>3.48778295516968</v>
+        <v>3.48778343200684</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G201" t="n">
-        <v>3.41095232963562</v>
+        <v>3.4109525680542</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G204" t="n">
-        <v>3.54860734939575</v>
+        <v>3.54860687255859</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G205" t="n">
-        <v>3.5149941444397</v>
+        <v>3.51499390602112</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G206" t="n">
-        <v>3.56461358070374</v>
+        <v>3.56461310386658</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G208" t="n">
-        <v>3.58382129669189</v>
+        <v>3.58382153511047</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G209" t="n">
-        <v>3.60943102836609</v>
+        <v>3.60943174362183</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.32600021362305</v>
       </c>
       <c r="G211" t="n">
-        <v>3.4621729850769</v>
+        <v>3.46217346191406</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G214" t="n">
-        <v>3.56141209602356</v>
+        <v>3.56141233444214</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>3.56141209602356</v>
+        <v>3.56141233444214</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G216" t="n">
-        <v>3.40935182571411</v>
+        <v>3.40935230255127</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G219" t="n">
-        <v>3.34692716598511</v>
+        <v>3.34692740440369</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G220" t="n">
-        <v>3.26529479026794</v>
+        <v>3.2652952671051</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G221" t="n">
-        <v>3.30050897598267</v>
+        <v>3.30050873756409</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.00600004196167</v>
       </c>
       <c r="G222" t="n">
-        <v>3.20607137680054</v>
+        <v>3.2060718536377</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.00600004196167</v>
       </c>
       <c r="G224" t="n">
-        <v>3.20607137680054</v>
+        <v>3.2060718536377</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G225" t="n">
-        <v>3.15325045585632</v>
+        <v>3.15325093269348</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G226" t="n">
-        <v>3.14204621315002</v>
+        <v>3.1420464515686</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G227" t="n">
-        <v>3.1100332736969</v>
+        <v>3.11003351211548</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G228" t="n">
-        <v>3.14524722099304</v>
+        <v>3.14524745941162</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.08122205734253</v>
+        <v>3.08122158050537</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G230" t="n">
-        <v>3.0476086139679</v>
+        <v>3.04760885238647</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G232" t="n">
-        <v>2.94196653366089</v>
+        <v>2.94196701049805</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G233" t="n">
-        <v>2.95317101478577</v>
+        <v>2.95317125320435</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G234" t="n">
-        <v>2.89074659347534</v>
+        <v>2.89074611663818</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G235" t="n">
-        <v>2.85713315010071</v>
+        <v>2.85713291168213</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G236" t="n">
-        <v>2.90195059776306</v>
+        <v>2.90195083618164</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G237" t="n">
-        <v>2.9051525592804</v>
+        <v>2.90515232086182</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G238" t="n">
-        <v>2.89394783973694</v>
+        <v>2.89394760131836</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G239" t="n">
-        <v>2.98358297348022</v>
+        <v>2.98358368873596</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G241" t="n">
-        <v>3.11963725090027</v>
+        <v>3.11963701248169</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G242" t="n">
-        <v>3.14524722099304</v>
+        <v>3.14524745941162</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G243" t="n">
-        <v>3.24928879737854</v>
+        <v>3.24928855895996</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G244" t="n">
-        <v>3.16605544090271</v>
+        <v>3.16605567932129</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G245" t="n">
-        <v>3.22848010063171</v>
+        <v>3.22848033905029</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G246" t="n">
-        <v>3.28130102157593</v>
+        <v>3.28130125999451</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>3.38534235954285</v>
+        <v>3.38534212112427</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G248" t="n">
-        <v>3.361332654953</v>
+        <v>3.36133289337158</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.26599979400635</v>
       </c>
       <c r="G249" t="n">
-        <v>3.4141538143158</v>
+        <v>3.41415333747864</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.22200012207031</v>
       </c>
       <c r="G250" t="n">
-        <v>3.37894034385681</v>
+        <v>3.37893986701965</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G251" t="n">
-        <v>3.40935182571411</v>
+        <v>3.40935230255127</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G253" t="n">
-        <v>3.42535901069641</v>
+        <v>3.42535877227783</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G254" t="n">
-        <v>3.49738740921021</v>
+        <v>3.49738693237305</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>3.44136500358582</v>
+        <v>3.44136476516724</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G260" t="n">
-        <v>3.54700660705566</v>
+        <v>3.54700708389282</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G261" t="n">
-        <v>3.54700660705566</v>
+        <v>3.54700708389282</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G262" t="n">
-        <v>3.51339364051819</v>
+        <v>3.51339316368103</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>4.32600021362305</v>
       </c>
       <c r="G264" t="n">
-        <v>3.4621729850769</v>
+        <v>3.46217346191406</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G266" t="n">
-        <v>3.62543773651123</v>
+        <v>3.62543797492981</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G268" t="n">
-        <v>3.41255331039429</v>
+        <v>3.41255307197571</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G269" t="n">
-        <v>3.26209354400635</v>
+        <v>3.26209378242493</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G271" t="n">
-        <v>3.15485119819641</v>
+        <v>3.15485095977783</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>3.15325045585632</v>
+        <v>3.15325093269348</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>3.16925716400146</v>
+        <v>3.16925668716431</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.00799989700317</v>
       </c>
       <c r="G282" t="n">
-        <v>3.20767164230347</v>
+        <v>3.20767188072205</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G284" t="n">
-        <v>3.08922481536865</v>
+        <v>3.08922505378723</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G286" t="n">
-        <v>3.16765642166138</v>
+        <v>3.16765594482422</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G288" t="n">
-        <v>3.44136500358582</v>
+        <v>3.44136476516724</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>4.89400005340576</v>
       </c>
       <c r="G290" t="n">
-        <v>3.9167537689209</v>
+        <v>3.91675329208374</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>3.96157121658325</v>
+        <v>3.96157145500183</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G292" t="n">
-        <v>4.04160308837891</v>
+        <v>4.04160356521606</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G294" t="n">
-        <v>4.08962249755859</v>
+        <v>4.08962202072144</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G297" t="n">
-        <v>3.87353610992432</v>
+        <v>3.8735363483429</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G298" t="n">
-        <v>4.10562801361084</v>
+        <v>4.105628490448</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G300" t="n">
-        <v>4.25368642807007</v>
+        <v>4.25368690490723</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G303" t="n">
-        <v>4.31771183013916</v>
+        <v>4.31771278381348</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>4.32171440124512</v>
+        <v>4.32171392440796</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G308" t="n">
-        <v>4.26969432830811</v>
+        <v>4.26969289779663</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G310" t="n">
-        <v>4.29370307922363</v>
+        <v>4.29370212554932</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G311" t="n">
-        <v>4.46577167510986</v>
+        <v>4.46577072143555</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G314" t="n">
-        <v>4.16565179824829</v>
+        <v>4.16565132141113</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G317" t="n">
-        <v>4.25768899917603</v>
+        <v>4.25768852233887</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G318" t="n">
-        <v>4.15364789962769</v>
+        <v>4.15364694595337</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G319" t="n">
-        <v>4.15764951705933</v>
+        <v>4.15764904022217</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G323" t="n">
-        <v>4.01759338378906</v>
+        <v>4.0175929069519</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>4.04160308837891</v>
+        <v>4.04160356521606</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G326" t="n">
-        <v>4.15364789962769</v>
+        <v>4.15364694595337</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G329" t="n">
-        <v>4.32171440124512</v>
+        <v>4.32171392440796</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>4.27369451522827</v>
+        <v>4.27369499206543</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>4.18565940856934</v>
+        <v>4.18565988540649</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>4.26969432830811</v>
+        <v>4.26969289779663</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G334" t="n">
-        <v>4.21367073059082</v>
+        <v>4.21367120742798</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G336" t="n">
-        <v>4.25368642807007</v>
+        <v>4.25368690490723</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>4.43375873565674</v>
+        <v>4.43375778198242</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G340" t="n">
-        <v>4.42575550079346</v>
+        <v>4.4257550239563</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.58181667327881</v>
+        <v>4.58181715011597</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G343" t="n">
-        <v>4.58181667327881</v>
+        <v>4.58181715011597</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>5.7649998664856</v>
       </c>
       <c r="G344" t="n">
-        <v>4.61382961273193</v>
+        <v>4.61383056640625</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.89499998092651</v>
       </c>
       <c r="G346" t="n">
-        <v>4.71787166595459</v>
+        <v>4.71787071228027</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>4.55380535125732</v>
+        <v>4.55380630493164</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G351" t="n">
-        <v>4.24568319320679</v>
+        <v>4.24568367004395</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G353" t="n">
-        <v>4.16965293884277</v>
+        <v>4.16965341567993</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>4.35572385787964</v>
+        <v>4.35572338104248</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G357" t="n">
-        <v>4.32309675216675</v>
+        <v>4.32309722900391</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G359" t="n">
-        <v>4.2741551399231</v>
+        <v>4.27415609359741</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G360" t="n">
-        <v>4.21297931671143</v>
+        <v>4.21298027038574</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G361" t="n">
-        <v>4.18443059921265</v>
+        <v>4.18443155288696</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G362" t="n">
-        <v>4.16811656951904</v>
+        <v>4.1681170463562</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G364" t="n">
-        <v>4.2741551399231</v>
+        <v>4.27415609359741</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>4.17627429962158</v>
+        <v>4.17627382278442</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>4.11917638778687</v>
+        <v>4.11917734146118</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>4.25376462936401</v>
+        <v>4.2537636756897</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G371" t="n">
-        <v>4.29862451553345</v>
+        <v>4.29862594604492</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>5.31500005722046</v>
       </c>
       <c r="G375" t="n">
-        <v>4.33533191680908</v>
+        <v>4.33533143997192</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>4.32309675216675</v>
+        <v>4.32309722900391</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G379" t="n">
-        <v>4.2904691696167</v>
+        <v>4.29046964645386</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G380" t="n">
-        <v>4.37203741073608</v>
+        <v>4.37203788757324</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>4.38835096359253</v>
+        <v>4.38835048675537</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G383" t="n">
-        <v>4.31493949890137</v>
+        <v>4.31493854522705</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G384" t="n">
-        <v>4.25784254074097</v>
+        <v>4.25784158706665</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>4.59226989746094</v>
+        <v>4.5922703742981</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>5.5</v>
       </c>
       <c r="G386" t="n">
-        <v>4.48623275756836</v>
+        <v>4.4862322807312</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6</v>
       </c>
       <c r="G388" t="n">
-        <v>4.89407157897949</v>
+        <v>4.89407110214233</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G390" t="n">
-        <v>5.00011014938354</v>
+        <v>5.00010967254639</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G391" t="n">
-        <v>5.13877487182617</v>
+        <v>5.13877439498901</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>5.13877487182617</v>
+        <v>5.13877439498901</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G394" t="n">
-        <v>5.14285326004028</v>
+        <v>5.14285278320312</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.5</v>
       </c>
       <c r="G395" t="n">
-        <v>5.30191087722778</v>
+        <v>5.30190944671631</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.36499977111816</v>
       </c>
       <c r="G396" t="n">
-        <v>5.1917929649353</v>
+        <v>5.19179391860962</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G398" t="n">
-        <v>5.23257827758789</v>
+        <v>5.23257780075073</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G402" t="n">
-        <v>5.18363666534424</v>
+        <v>5.1836371421814</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G405" t="n">
-        <v>4.91038465499878</v>
+        <v>4.91038513183594</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G406" t="n">
-        <v>4.94709014892578</v>
+        <v>4.94709062576294</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>5.01642274856567</v>
+        <v>5.01642370223999</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G408" t="n">
-        <v>5.13877487182617</v>
+        <v>5.13877439498901</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G414" t="n">
-        <v>4.85328769683838</v>
+        <v>4.85328722000122</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G415" t="n">
-        <v>4.85328769683838</v>
+        <v>4.85328722000122</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G418" t="n">
-        <v>4.80434656143188</v>
+        <v>4.80434703826904</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G419" t="n">
-        <v>4.83697319030762</v>
+        <v>4.83697366714478</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G420" t="n">
-        <v>4.7880334854126</v>
+        <v>4.78803205490112</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G421" t="n">
-        <v>4.80026769638062</v>
+        <v>4.80026817321777</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G422" t="n">
-        <v>4.84920883178711</v>
+        <v>4.84920930862427</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>4.81250381469727</v>
+        <v>4.81250333786011</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G425" t="n">
-        <v>4.918541431427</v>
+        <v>4.91854190826416</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>6</v>
       </c>
       <c r="G426" t="n">
-        <v>4.89407157897949</v>
+        <v>4.89407110214233</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G427" t="n">
-        <v>4.94301176071167</v>
+        <v>4.94301223754883</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G428" t="n">
-        <v>5.00826644897461</v>
+        <v>5.00826549530029</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>5.06536340713501</v>
+        <v>5.06536483764648</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G432" t="n">
-        <v>5.02458047866821</v>
+        <v>5.02458000183105</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.13877487182617</v>
+        <v>5.13877439498901</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G435" t="n">
-        <v>5.13877487182617</v>
+        <v>5.13877439498901</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G436" t="n">
-        <v>5.22034311294556</v>
+        <v>5.22034215927124</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G437" t="n">
-        <v>5.15508890151978</v>
+        <v>5.15508842468262</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G438" t="n">
-        <v>5.11430501937866</v>
+        <v>5.1143045425415</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>5.46504545211792</v>
+        <v>5.46504592895508</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G441" t="n">
-        <v>5.87696409225464</v>
+        <v>5.8769645690918</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G442" t="n">
-        <v>5.68527984619141</v>
+        <v>5.68527936935425</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>5.87696409225464</v>
+        <v>5.8769645690918</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>5.94629716873169</v>
+        <v>5.94629669189453</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G446" t="n">
-        <v>6.03602123260498</v>
+        <v>6.03602170944214</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G447" t="n">
-        <v>5.76684761047363</v>
+        <v>5.76684808731079</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G448" t="n">
-        <v>5.81578779220581</v>
+        <v>5.81578874588013</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G449" t="n">
-        <v>5.84025812149048</v>
+        <v>5.84025859832764</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G450" t="n">
-        <v>5.90551233291626</v>
+        <v>5.90551280975342</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G451" t="n">
-        <v>5.84025812149048</v>
+        <v>5.84025859832764</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G452" t="n">
-        <v>5.86880779266357</v>
+        <v>5.86880731582642</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>5.79131746292114</v>
+        <v>5.7913179397583</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G455" t="n">
-        <v>5.73829889297485</v>
+        <v>5.73829793930054</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G456" t="n">
-        <v>5.80355310440063</v>
+        <v>5.80355262756348</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G457" t="n">
-        <v>5.77500438690186</v>
+        <v>5.7750039100647</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G459" t="n">
-        <v>5.75053358078003</v>
+        <v>5.75053405761719</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G460" t="n">
-        <v>5.72198534011841</v>
+        <v>5.72198486328125</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G461" t="n">
-        <v>5.84025812149048</v>
+        <v>5.84025859832764</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G463" t="n">
-        <v>5.85657167434692</v>
+        <v>5.85657215118408</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>5.90959119796753</v>
+        <v>5.90959167480469</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G465" t="n">
-        <v>5.96260976791382</v>
+        <v>5.96261024475098</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G466" t="n">
-        <v>5.86880779266357</v>
+        <v>5.86880731582642</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G467" t="n">
-        <v>5.90143442153931</v>
+        <v>5.90143394470215</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G468" t="n">
-        <v>5.87288570404053</v>
+        <v>5.87288522720337</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G469" t="n">
-        <v>5.92182683944702</v>
+        <v>5.92182636260986</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G470" t="n">
-        <v>5.95037508010864</v>
+        <v>5.9503755569458</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>6.15837335586548</v>
+        <v>6.15837287902832</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>6.0441780090332</v>
+        <v>6.04417753219604</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>6.03602123260498</v>
+        <v>6.03602170944214</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G474" t="n">
-        <v>6.06864881515503</v>
+        <v>6.06864833831787</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G476" t="n">
-        <v>6.06864881515503</v>
+        <v>6.06864833831787</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G477" t="n">
-        <v>6.1135106086731</v>
+        <v>6.11351108551025</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G479" t="n">
-        <v>5.8973560333252</v>
+        <v>5.89735651016235</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G480" t="n">
-        <v>5.95037508010864</v>
+        <v>5.9503755569458</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>5.87696409225464</v>
+        <v>5.8769645690918</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G482" t="n">
-        <v>5.9707670211792</v>
+        <v>5.97076749801636</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>6.05233478546143</v>
+        <v>6.05233573913574</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G484" t="n">
-        <v>6.07680511474609</v>
+        <v>6.07680463790894</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G485" t="n">
-        <v>6.08904027938843</v>
+        <v>6.08903980255127</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>7.375</v>
       </c>
       <c r="G486" t="n">
-        <v>6.01562929153442</v>
+        <v>6.01562976837158</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G487" t="n">
-        <v>5.92182683944702</v>
+        <v>5.92182636260986</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G489" t="n">
-        <v>5.87288570404053</v>
+        <v>5.87288522720337</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G492" t="n">
-        <v>5.81986665725708</v>
+        <v>5.81986618041992</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G493" t="n">
-        <v>5.81578779220581</v>
+        <v>5.81578874588013</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G494" t="n">
-        <v>5.88512134552002</v>
+        <v>5.88512086868286</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G495" t="n">
-        <v>5.87288570404053</v>
+        <v>5.87288522720337</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G496" t="n">
-        <v>5.85657167434692</v>
+        <v>5.85657215118408</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G498" t="n">
-        <v>5.90143442153931</v>
+        <v>5.90143394470215</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>5.87288570404053</v>
+        <v>5.87288522720337</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>5.90959119796753</v>
+        <v>5.90959167480469</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G504" t="n">
-        <v>5.9870810508728</v>
+        <v>5.98708057403564</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>7.25</v>
       </c>
       <c r="G506" t="n">
-        <v>5.91366910934448</v>
+        <v>5.91366863250732</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G507" t="n">
-        <v>6.01970815658569</v>
+        <v>6.01970767974854</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G508" t="n">
-        <v>5.96668815612793</v>
+        <v>5.96668863296509</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>6.06864881515503</v>
+        <v>6.06864833831787</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G511" t="n">
-        <v>6.15837335586548</v>
+        <v>6.15837287902832</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G512" t="n">
-        <v>6.0931191444397</v>
+        <v>6.09311866760254</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G515" t="n">
-        <v>6.476487159729</v>
+        <v>6.47648763656616</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G517" t="n">
-        <v>6.37045001983643</v>
+        <v>6.37044906616211</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G518" t="n">
-        <v>6.36229276657104</v>
+        <v>6.3622932434082</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>6.37045001983643</v>
+        <v>6.37044906616211</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G520" t="n">
-        <v>6.51727199554443</v>
+        <v>6.51727104187012</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G521" t="n">
-        <v>6.59883975982666</v>
+        <v>6.59883880615234</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>6.45201826095581</v>
+        <v>6.45201683044434</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G526" t="n">
-        <v>6.49280118942261</v>
+        <v>6.49280166625977</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G528" t="n">
-        <v>6.38676309585571</v>
+        <v>6.38676404953003</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>8</v>
       </c>
       <c r="G530" t="n">
-        <v>6.5254282951355</v>
+        <v>6.52542781829834</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G531" t="n">
-        <v>6.41123247146606</v>
+        <v>6.41123390197754</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G534" t="n">
-        <v>6.10127639770508</v>
+        <v>6.10127544403076</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>6.03602123260498</v>
+        <v>6.03602170944214</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G536" t="n">
-        <v>5.90551233291626</v>
+        <v>5.90551280975342</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G539" t="n">
-        <v>5.79131746292114</v>
+        <v>5.7913179397583</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G540" t="n">
-        <v>5.80763149261475</v>
+        <v>5.80763101577759</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>5.87288570404053</v>
+        <v>5.87288522720337</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G542" t="n">
-        <v>5.84025812149048</v>
+        <v>5.84025859832764</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G544" t="n">
-        <v>6.03602123260498</v>
+        <v>6.03602170944214</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G545" t="n">
-        <v>6.0931191444397</v>
+        <v>6.09311866760254</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G546" t="n">
-        <v>6.13390254974365</v>
+        <v>6.13390302658081</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G549" t="n">
-        <v>6.19915628433228</v>
+        <v>6.19915676116943</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>6.07680511474609</v>
+        <v>6.07680463790894</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G552" t="n">
-        <v>6.01155138015747</v>
+        <v>6.01155042648315</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G556" t="n">
-        <v>5.82394409179688</v>
+        <v>5.82394456863403</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G557" t="n">
-        <v>5.8973560333252</v>
+        <v>5.89735651016235</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G558" t="n">
-        <v>5.92182683944702</v>
+        <v>5.92182636260986</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G559" t="n">
-        <v>6.07680511474609</v>
+        <v>6.07680463790894</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G560" t="n">
-        <v>6.00339412689209</v>
+        <v>6.00339508056641</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G561" t="n">
-        <v>6.13390254974365</v>
+        <v>6.13390302658081</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G563" t="n">
-        <v>5.82394409179688</v>
+        <v>5.82394456863403</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G565" t="n">
-        <v>5.80763149261475</v>
+        <v>5.80763101577759</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G566" t="n">
-        <v>5.79131746292114</v>
+        <v>5.7913179397583</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G567" t="n">
-        <v>5.75869035720825</v>
+        <v>5.75868988037109</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G568" t="n">
-        <v>5.82394409179688</v>
+        <v>5.82394456863403</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G569" t="n">
-        <v>5.72606325149536</v>
+        <v>5.7260627746582</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G571" t="n">
-        <v>5.60371208190918</v>
+        <v>5.60371160507202</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G572" t="n">
-        <v>5.63633918762207</v>
+        <v>5.63633871078491</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G573" t="n">
-        <v>5.63633918762207</v>
+        <v>5.63633871078491</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G574" t="n">
-        <v>5.75053358078003</v>
+        <v>5.75053405761719</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G577" t="n">
-        <v>5.92182683944702</v>
+        <v>5.92182636260986</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G578" t="n">
-        <v>5.9870810508728</v>
+        <v>5.98708057403564</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G579" t="n">
-        <v>5.90551233291626</v>
+        <v>5.90551280975342</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G581" t="n">
-        <v>5.82394409179688</v>
+        <v>5.82394456863403</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G582" t="n">
-        <v>5.84025812149048</v>
+        <v>5.84025859832764</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G583" t="n">
-        <v>5.85657167434692</v>
+        <v>5.85657215118408</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G584" t="n">
-        <v>5.76684761047363</v>
+        <v>5.76684808731079</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G585" t="n">
-        <v>5.79131746292114</v>
+        <v>5.7913179397583</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>5.75053358078003</v>
+        <v>5.75053405761719</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G594" t="n">
-        <v>5.65265274047852</v>
+        <v>5.65265226364136</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G595" t="n">
-        <v>5.81578779220581</v>
+        <v>5.81578874588013</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G598" t="n">
-        <v>5.9707670211792</v>
+        <v>5.97076749801636</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G599" t="n">
-        <v>5.8973560333252</v>
+        <v>5.89735651016235</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G600" t="n">
-        <v>5.90551233291626</v>
+        <v>5.90551280975342</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>5.87288570404053</v>
+        <v>5.87288522720337</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>5.96260976791382</v>
+        <v>5.96261024475098</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G605" t="n">
-        <v>5.66080951690674</v>
+        <v>5.66080856323242</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G607" t="n">
-        <v>5.51398706436157</v>
+        <v>5.51398754119873</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G608" t="n">
-        <v>5.53054571151733</v>
+        <v>5.53054618835449</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G610" t="n">
-        <v>5.5471043586731</v>
+        <v>5.54710388183594</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G611" t="n">
-        <v>5.5802206993103</v>
+        <v>5.58022117614746</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G612" t="n">
-        <v>5.53054571151733</v>
+        <v>5.53054618835449</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G613" t="n">
-        <v>5.36496114730835</v>
+        <v>5.36496019363403</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>5.34012269973755</v>
+        <v>5.34012317657471</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G616" t="n">
-        <v>5.4229154586792</v>
+        <v>5.42291593551636</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>5.62161731719971</v>
+        <v>5.62161779403687</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G619" t="n">
-        <v>5.53054571151733</v>
+        <v>5.53054618835449</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G620" t="n">
-        <v>5.53882503509521</v>
+        <v>5.53882455825806</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>5.65473508834839</v>
+        <v>5.65473461151123</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G623" t="n">
-        <v>5.78720188140869</v>
+        <v>5.78720283508301</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G625" t="n">
-        <v>5.7706446647644</v>
+        <v>5.77064418792725</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G626" t="n">
-        <v>5.6298975944519</v>
+        <v>5.62989711761475</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G627" t="n">
-        <v>5.66301441192627</v>
+        <v>5.66301393508911</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>5.66301441192627</v>
+        <v>5.66301393508911</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G629" t="n">
-        <v>5.59678030014038</v>
+        <v>5.59677982330322</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G633" t="n">
-        <v>5.36496114730835</v>
+        <v>5.36496019363403</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G636" t="n">
-        <v>5.60505962371826</v>
+        <v>5.6050591468811</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G637" t="n">
-        <v>5.61333799362183</v>
+        <v>5.61333847045898</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G638" t="n">
-        <v>5.48914861679077</v>
+        <v>5.48914957046509</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G640" t="n">
-        <v>5.55538320541382</v>
+        <v>5.55538368225098</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G641" t="n">
-        <v>5.78720188140869</v>
+        <v>5.78720283508301</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G642" t="n">
-        <v>5.88655376434326</v>
+        <v>5.88655424118042</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G643" t="n">
-        <v>5.8699951171875</v>
+        <v>5.86999559402466</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G646" t="n">
-        <v>5.69613075256348</v>
+        <v>5.69613122940063</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G647" t="n">
-        <v>5.63817644119263</v>
+        <v>5.63817596435547</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G648" t="n">
-        <v>5.67957210540771</v>
+        <v>5.67957258224487</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G649" t="n">
-        <v>5.6298975944519</v>
+        <v>5.62989711761475</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G650" t="n">
-        <v>5.67129278182983</v>
+        <v>5.67129325866699</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>5.62161731719971</v>
+        <v>5.62161779403687</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G654" t="n">
-        <v>5.53882503509521</v>
+        <v>5.53882455825806</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G656" t="n">
-        <v>5.62161731719971</v>
+        <v>5.62161779403687</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G657" t="n">
-        <v>5.62161731719971</v>
+        <v>5.62161779403687</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G659" t="n">
-        <v>5.75408506393433</v>
+        <v>5.75408554077148</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G660" t="n">
-        <v>5.80376100540161</v>
+        <v>5.80376195907593</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G663" t="n">
-        <v>5.70441007614136</v>
+        <v>5.70440912246704</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G664" t="n">
-        <v>5.78720188140869</v>
+        <v>5.78720283508301</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>5.71268939971924</v>
+        <v>5.7126898765564</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G666" t="n">
-        <v>5.6298975944519</v>
+        <v>5.62989711761475</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>5.36496114730835</v>
+        <v>5.36496019363403</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G669" t="n">
-        <v>5.2738881111145</v>
+        <v>5.27388858795166</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G670" t="n">
-        <v>5.22421360015869</v>
+        <v>5.22421312332153</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G671" t="n">
-        <v>5.14969921112061</v>
+        <v>5.14969968795776</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>5.34840202331543</v>
+        <v>5.34840154647827</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>5.24077129364014</v>
+        <v>5.24077224731445</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G678" t="n">
-        <v>5.25733041763306</v>
+        <v>5.2573299407959</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G679" t="n">
-        <v>5.22421360015869</v>
+        <v>5.22421312332153</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G680" t="n">
-        <v>5.11658239364624</v>
+        <v>5.1165828704834</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G681" t="n">
-        <v>5.03379058837891</v>
+        <v>5.03378963470459</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G682" t="n">
-        <v>5.14969921112061</v>
+        <v>5.14969968795776</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G683" t="n">
-        <v>5.00895309448242</v>
+        <v>5.00895261764526</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G684" t="n">
-        <v>5.11658239364624</v>
+        <v>5.1165828704834</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G687" t="n">
-        <v>5.1579794883728</v>
+        <v>5.15797901153564</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G689" t="n">
-        <v>5.10002470016479</v>
+        <v>5.10002374649048</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G690" t="n">
-        <v>5.12486267089844</v>
+        <v>5.12486171722412</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>6.25</v>
       </c>
       <c r="G691" t="n">
-        <v>5.17453718185425</v>
+        <v>5.17453765869141</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>5.20765399932861</v>
+        <v>5.20765447616577</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G695" t="n">
-        <v>5.21593332290649</v>
+        <v>5.21593379974365</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>5.20765399932861</v>
+        <v>5.20765447616577</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G699" t="n">
-        <v>5.14969921112061</v>
+        <v>5.14969968795776</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G700" t="n">
-        <v>5.05862903594971</v>
+        <v>5.05862855911255</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G701" t="n">
-        <v>4.98411417007446</v>
+        <v>4.98411464691162</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G702" t="n">
-        <v>5.03379058837891</v>
+        <v>5.03378963470459</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>5.06690788269043</v>
+        <v>5.06690740585327</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>5.00067329406738</v>
+        <v>5.00067281723022</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G705" t="n">
-        <v>4.98411417007446</v>
+        <v>4.98411464691162</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G706" t="n">
-        <v>4.81024980545044</v>
+        <v>4.81024932861328</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G707" t="n">
-        <v>4.50391721725464</v>
+        <v>4.5039176940918</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G711" t="n">
-        <v>4.44596290588379</v>
+        <v>4.44596242904663</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>4.52047634124756</v>
+        <v>4.5204758644104</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G715" t="n">
-        <v>4.37144899368286</v>
+        <v>4.37144947052002</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G717" t="n">
-        <v>4.05683708190918</v>
+        <v>4.05683755874634</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G720" t="n">
-        <v>4.1147928237915</v>
+        <v>4.11479234695435</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G721" t="n">
-        <v>4.06925630569458</v>
+        <v>4.06925678253174</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G722" t="n">
-        <v>4.30521488189697</v>
+        <v>4.30521535873413</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G723" t="n">
-        <v>4.43768358230591</v>
+        <v>4.43768405914307</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>4.51219606399536</v>
+        <v>4.51219654083252</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G728" t="n">
-        <v>4.50391721725464</v>
+        <v>4.5039176940918</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G729" t="n">
-        <v>4.43768358230591</v>
+        <v>4.43768405914307</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G731" t="n">
-        <v>4.39628744125366</v>
+        <v>4.3962869644165</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G733" t="n">
-        <v>4.3383321762085</v>
+        <v>4.33833265304565</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>4.20586442947388</v>
+        <v>4.20586395263672</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G736" t="n">
-        <v>4.24726009368896</v>
+        <v>4.24726057052612</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G738" t="n">
-        <v>3.96162605285645</v>
+        <v>3.96162581443787</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G740" t="n">
-        <v>4.01958036422729</v>
+        <v>4.01958084106445</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G741" t="n">
-        <v>4.0651159286499</v>
+        <v>4.06511688232422</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G742" t="n">
-        <v>4.14791011810303</v>
+        <v>4.14790964126587</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G743" t="n">
-        <v>4.1272120475769</v>
+        <v>4.12721109390259</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>4.01544094085693</v>
+        <v>4.01544141769409</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>3.95334625244141</v>
+        <v>3.95334672927856</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G749" t="n">
-        <v>4.1147928237915</v>
+        <v>4.11479234695435</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G750" t="n">
-        <v>4.01958036422729</v>
+        <v>4.01958084106445</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>4.05269718170166</v>
+        <v>4.05269765853882</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G754" t="n">
-        <v>4.0651159286499</v>
+        <v>4.06511688232422</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>3.86227488517761</v>
+        <v>3.86227464675903</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G759" t="n">
-        <v>4.06925630569458</v>
+        <v>4.06925678253174</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G760" t="n">
-        <v>4.05683708190918</v>
+        <v>4.05683755874634</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G764" t="n">
-        <v>4.22242259979248</v>
+        <v>4.22242212295532</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G766" t="n">
-        <v>4.37144899368286</v>
+        <v>4.37144947052002</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G767" t="n">
-        <v>4.39628744125366</v>
+        <v>4.3962869644165</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>4.51219606399536</v>
+        <v>4.51219654083252</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G770" t="n">
-        <v>4.52047634124756</v>
+        <v>4.5204758644104</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>4.52047634124756</v>
+        <v>4.5204758644104</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G772" t="n">
-        <v>4.51219606399536</v>
+        <v>4.51219654083252</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>5.5</v>
       </c>
       <c r="G773" t="n">
-        <v>4.55359268188477</v>
+        <v>4.55359315872192</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>4.69434070587158</v>
+        <v>4.69434022903442</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G775" t="n">
-        <v>4.6860613822937</v>
+        <v>4.68606090545654</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G776" t="n">
-        <v>4.71917819976807</v>
+        <v>4.71917772293091</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.75</v>
       </c>
       <c r="G777" t="n">
-        <v>4.76057481765747</v>
+        <v>4.76057434082031</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.75</v>
       </c>
       <c r="G780" t="n">
-        <v>4.76057481765747</v>
+        <v>4.76057434082031</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G781" t="n">
-        <v>4.78541278839111</v>
+        <v>4.78541231155396</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G782" t="n">
-        <v>4.85164642333984</v>
+        <v>4.85164594650269</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G783" t="n">
-        <v>4.90132188796997</v>
+        <v>4.90132236480713</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G784" t="n">
-        <v>4.90960073471069</v>
+        <v>4.90960121154785</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G787" t="n">
-        <v>4.90960073471069</v>
+        <v>4.90960121154785</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G789" t="n">
-        <v>4.9509973526001</v>
+        <v>4.95099782943726</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G791" t="n">
-        <v>4.86820459365845</v>
+        <v>4.86820507049561</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G793" t="n">
-        <v>4.98411417007446</v>
+        <v>4.98411464691162</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G795" t="n">
-        <v>5.10002470016479</v>
+        <v>5.10002374649048</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G797" t="n">
-        <v>5.21593332290649</v>
+        <v>5.21593379974365</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G798" t="n">
-        <v>5.09174537658691</v>
+        <v>5.09174489974976</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>5.03379058837891</v>
+        <v>5.03378963470459</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G800" t="n">
-        <v>5.01723098754883</v>
+        <v>5.01723194122314</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G801" t="n">
-        <v>5.05862903594971</v>
+        <v>5.05862855911255</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G802" t="n">
-        <v>5.06690788269043</v>
+        <v>5.06690740585327</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>5.05034828186035</v>
+        <v>5.05034875869751</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G805" t="n">
-        <v>5.06690788269043</v>
+        <v>5.06690740585327</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G806" t="n">
-        <v>5.11658239364624</v>
+        <v>5.1165828704834</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G808" t="n">
-        <v>5.12486267089844</v>
+        <v>5.12486171722412</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G809" t="n">
-        <v>5.12486267089844</v>
+        <v>5.12486171722412</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G811" t="n">
-        <v>5.05034828186035</v>
+        <v>5.05034875869751</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G812" t="n">
-        <v>5.12486267089844</v>
+        <v>5.12486171722412</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G813" t="n">
-        <v>5.23249244689941</v>
+        <v>5.23249292373657</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G815" t="n">
-        <v>5.16625881195068</v>
+        <v>5.16625833511353</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G816" t="n">
-        <v>5.14969921112061</v>
+        <v>5.14969968795776</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G820" t="n">
-        <v>5.34012269973755</v>
+        <v>5.34012317657471</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G821" t="n">
-        <v>5.29044771194458</v>
+        <v>5.29044723510742</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G822" t="n">
-        <v>5.10002470016479</v>
+        <v>5.10002374649048</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G823" t="n">
-        <v>5.09174537658691</v>
+        <v>5.09174489974976</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G824" t="n">
-        <v>5.22421360015869</v>
+        <v>5.22421312332153</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>5.20765399932861</v>
+        <v>5.20765447616577</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>5.20765399932861</v>
+        <v>5.20765447616577</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G827" t="n">
-        <v>5.28216791152954</v>
+        <v>5.28216743469238</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G828" t="n">
-        <v>5.34012269973755</v>
+        <v>5.34012317657471</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G831" t="n">
-        <v>5.35668134689331</v>
+        <v>5.35668182373047</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G832" t="n">
-        <v>5.34012269973755</v>
+        <v>5.34012317657471</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>6.5</v>
       </c>
       <c r="G833" t="n">
-        <v>5.38151884078979</v>
+        <v>5.38151836395264</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G835" t="n">
-        <v>5.35668134689331</v>
+        <v>5.35668182373047</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>6.5</v>
       </c>
       <c r="G837" t="n">
-        <v>5.38151884078979</v>
+        <v>5.38151836395264</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G840" t="n">
-        <v>5.2987265586853</v>
+        <v>5.29872608184814</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>5.2738881111145</v>
+        <v>5.27388858795166</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G844" t="n">
-        <v>5.2738881111145</v>
+        <v>5.27388858795166</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>5.34840202331543</v>
+        <v>5.34840154647827</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G846" t="n">
-        <v>5.35668134689331</v>
+        <v>5.35668182373047</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>6.5</v>
       </c>
       <c r="G847" t="n">
-        <v>5.38151884078979</v>
+        <v>5.38151836395264</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G848" t="n">
-        <v>5.4229154586792</v>
+        <v>5.42291593551636</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G849" t="n">
-        <v>5.28216791152954</v>
+        <v>5.28216743469238</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>5.14969921112061</v>
+        <v>5.14969968795776</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G851" t="n">
-        <v>5.23249244689941</v>
+        <v>5.23249292373657</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>5.21593332290649</v>
+        <v>5.21593379974365</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G854" t="n">
-        <v>5.01723098754883</v>
+        <v>5.01723194122314</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G855" t="n">
-        <v>5.05034828186035</v>
+        <v>5.05034875869751</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G856" t="n">
-        <v>4.87648439407349</v>
+        <v>4.87648391723633</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G857" t="n">
-        <v>5.05862903594971</v>
+        <v>5.05862855911255</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G859" t="n">
-        <v>5.00664472579956</v>
+        <v>5.00664520263672</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>5.00664472579956</v>
+        <v>5.00664520263672</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G862" t="n">
-        <v>4.91345930099487</v>
+        <v>4.91345977783203</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G863" t="n">
-        <v>4.91345930099487</v>
+        <v>4.91345977783203</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G864" t="n">
-        <v>4.90498781204224</v>
+        <v>4.90498828887939</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G867" t="n">
-        <v>4.9897027015686</v>
+        <v>4.98970317840576</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G870" t="n">
-        <v>5.00664472579956</v>
+        <v>5.00664520263672</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G872" t="n">
-        <v>5.09136009216309</v>
+        <v>5.09136056900024</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G873" t="n">
-        <v>5.06594610214233</v>
+        <v>5.06594562530518</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>5.1506609916687</v>
+        <v>5.15066051483154</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G879" t="n">
-        <v>5.14218950271606</v>
+        <v>5.14218902587891</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G880" t="n">
-        <v>5.22690391540527</v>
+        <v>5.22690343856812</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G881" t="n">
-        <v>5.22690391540527</v>
+        <v>5.22690343856812</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G883" t="n">
-        <v>5.4302191734314</v>
+        <v>5.43021965026855</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G884" t="n">
-        <v>5.3116192817688</v>
+        <v>5.31161880493164</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G885" t="n">
-        <v>5.21843290328979</v>
+        <v>5.21843242645264</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G887" t="n">
-        <v>5.45563459396362</v>
+        <v>5.45563411712646</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G888" t="n">
-        <v>5.4048056602478</v>
+        <v>5.40480470657349</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G890" t="n">
-        <v>5.4048056602478</v>
+        <v>5.40480470657349</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>5.52340602874756</v>
+        <v>5.5234055519104</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G892" t="n">
-        <v>5.64200592041016</v>
+        <v>5.64200687408447</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G894" t="n">
-        <v>5.60811996459961</v>
+        <v>5.60812091827393</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G900" t="n">
-        <v>5.52340602874756</v>
+        <v>5.5234055519104</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G901" t="n">
-        <v>5.48104810714722</v>
+        <v>5.48104858398438</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G903" t="n">
-        <v>5.33703279495239</v>
+        <v>5.33703327178955</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G904" t="n">
-        <v>5.4048056602478</v>
+        <v>5.40480470657349</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G905" t="n">
-        <v>5.44716215133667</v>
+        <v>5.44716262817383</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G906" t="n">
-        <v>5.6165919303894</v>
+        <v>5.61659240722656</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G909" t="n">
-        <v>5.60811996459961</v>
+        <v>5.60812091827393</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G910" t="n">
-        <v>5.44716215133667</v>
+        <v>5.44716262817383</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G911" t="n">
-        <v>5.39633369445801</v>
+        <v>5.39633321762085</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G913" t="n">
-        <v>5.14218950271606</v>
+        <v>5.14218902587891</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G915" t="n">
-        <v>5.09136009216309</v>
+        <v>5.09136056900024</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G916" t="n">
-        <v>5.07441711425781</v>
+        <v>5.07441759109497</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>6</v>
       </c>
       <c r="G919" t="n">
-        <v>5.08288908004761</v>
+        <v>5.08288955688477</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>5.06594610214233</v>
+        <v>5.06594562530518</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G926" t="n">
-        <v>5.09136009216309</v>
+        <v>5.09136056900024</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G929" t="n">
-        <v>5.09136009216309</v>
+        <v>5.09136056900024</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G931" t="n">
-        <v>5.09136009216309</v>
+        <v>5.09136056900024</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G933" t="n">
-        <v>5.05747413635254</v>
+        <v>5.05747365951538</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>5.4048056602478</v>
+        <v>5.40480470657349</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G941" t="n">
-        <v>5.32856178283691</v>
+        <v>5.32856130599976</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>5.32856178283691</v>
+        <v>5.32856130599976</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G944" t="n">
-        <v>5.28620481491089</v>
+        <v>5.28620433807373</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G946" t="n">
-        <v>5.4048056602478</v>
+        <v>5.40480470657349</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G947" t="n">
-        <v>5.28620481491089</v>
+        <v>5.28620433807373</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>6</v>
       </c>
       <c r="G949" t="n">
-        <v>5.08288908004761</v>
+        <v>5.08288955688477</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G950" t="n">
-        <v>5.1506609916687</v>
+        <v>5.15066051483154</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G952" t="n">
-        <v>5.09136009216309</v>
+        <v>5.09136056900024</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G953" t="n">
-        <v>5.20996189117432</v>
+        <v>5.20996141433716</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G954" t="n">
-        <v>5.2692608833313</v>
+        <v>5.26926136016846</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G956" t="n">
-        <v>4.92193031311035</v>
+        <v>4.92193078994751</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>5.05323839187622</v>
+        <v>5.05323886871338</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>5.82299995422363</v>
       </c>
       <c r="G959" t="n">
-        <v>4.93294334411621</v>
+        <v>4.93294286727905</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>6</v>
       </c>
       <c r="G964" t="n">
-        <v>5.08288908004761</v>
+        <v>5.08288955688477</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G966" t="n">
-        <v>5.16760349273682</v>
+        <v>5.16760396957397</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G967" t="n">
-        <v>5.16760349273682</v>
+        <v>5.16760396957397</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>6.17700004577637</v>
       </c>
       <c r="G968" t="n">
-        <v>5.23283433914185</v>
+        <v>5.23283386230469</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G969" t="n">
-        <v>5.21419668197632</v>
+        <v>5.21419715881348</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>6.10099983215332</v>
       </c>
       <c r="G970" t="n">
-        <v>5.16845083236694</v>
+        <v>5.16845035552979</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>6.13100004196167</v>
       </c>
       <c r="G971" t="n">
-        <v>5.19386529922485</v>
+        <v>5.19386577606201</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>6.08699989318848</v>
       </c>
       <c r="G972" t="n">
-        <v>5.15659046173096</v>
+        <v>5.15659093856812</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G973" t="n">
-        <v>5.21843290328979</v>
+        <v>5.21843242645264</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>6.17899990081787</v>
       </c>
       <c r="G974" t="n">
-        <v>5.2345290184021</v>
+        <v>5.23452806472778</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>6.17899990081787</v>
       </c>
       <c r="G975" t="n">
-        <v>5.2345290184021</v>
+        <v>5.23452806472778</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>6.17399978637695</v>
       </c>
       <c r="G977" t="n">
-        <v>5.23029279708862</v>
+        <v>5.23029232025146</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>6.33799982070923</v>
       </c>
       <c r="G978" t="n">
-        <v>5.36922454833984</v>
+        <v>5.369225025177</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>6.33799982070923</v>
       </c>
       <c r="G979" t="n">
-        <v>5.36922454833984</v>
+        <v>5.369225025177</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G980" t="n">
-        <v>5.32432556152344</v>
+        <v>5.32432508468628</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G981" t="n">
-        <v>5.20572519302368</v>
+        <v>5.20572566986084</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G982" t="n">
-        <v>5.32432556152344</v>
+        <v>5.32432508468628</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>6.37599992752075</v>
       </c>
       <c r="G983" t="n">
-        <v>5.40141630172729</v>
+        <v>5.40141677856445</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G984" t="n">
-        <v>5.49799108505249</v>
+        <v>5.49799060821533</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>6.33799982070923</v>
       </c>
       <c r="G986" t="n">
-        <v>5.36922454833984</v>
+        <v>5.369225025177</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>6.37400007247925</v>
       </c>
       <c r="G987" t="n">
-        <v>5.39972162246704</v>
+        <v>5.3997220993042</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>6.26599979400635</v>
       </c>
       <c r="G989" t="n">
-        <v>5.30822992324829</v>
+        <v>5.30823040008545</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>6.31799983978271</v>
       </c>
       <c r="G990" t="n">
-        <v>5.35228109359741</v>
+        <v>5.35228204727173</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>6.29099988937378</v>
       </c>
       <c r="G991" t="n">
-        <v>5.32940864562988</v>
+        <v>5.32940912246704</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G992" t="n">
-        <v>5.35397624969482</v>
+        <v>5.35397672653198</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G993" t="n">
-        <v>5.39633369445801</v>
+        <v>5.39633321762085</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>5.89615106582642</v>
+        <v>5.89615154266357</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G997" t="n">
-        <v>5.92156505584717</v>
+        <v>5.92156553268433</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>6.86899995803833</v>
       </c>
       <c r="G998" t="n">
-        <v>5.81906032562256</v>
+        <v>5.81906080245972</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>6.66699981689453</v>
       </c>
       <c r="G999" t="n">
-        <v>5.64793634414673</v>
+        <v>5.64793586730957</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>6.64900016784668</v>
       </c>
       <c r="G1001" t="n">
-        <v>5.63268756866455</v>
+        <v>5.63268804550171</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>6.63399982452393</v>
       </c>
       <c r="G1002" t="n">
-        <v>5.61997985839844</v>
+        <v>5.61998081207275</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>6.63199996948242</v>
       </c>
       <c r="G1003" t="n">
-        <v>5.61828660964966</v>
+        <v>5.6182861328125</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>6.82399988174438</v>
       </c>
       <c r="G1005" t="n">
-        <v>5.78093910217285</v>
+        <v>5.78093814849854</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1007" t="n">
-        <v>5.81567144393921</v>
+        <v>5.81567192077637</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>6.56400012969971</v>
       </c>
       <c r="G1012" t="n">
-        <v>5.56068086624146</v>
+        <v>5.5606803894043</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1014" t="n">
-        <v>5.64200592041016</v>
+        <v>5.64200687408447</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>6.72399997711182</v>
       </c>
       <c r="G1015" t="n">
-        <v>5.69622373580933</v>
+        <v>5.69622421264648</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1016" t="n">
-        <v>5.78178548812866</v>
+        <v>5.78178596496582</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>6.59299993515015</v>
       </c>
       <c r="G1017" t="n">
-        <v>5.58524751663208</v>
+        <v>5.58524799346924</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>6.65100002288818</v>
       </c>
       <c r="G1019" t="n">
-        <v>5.63438272476196</v>
+        <v>5.6343822479248</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1020" t="n">
-        <v>5.69283533096313</v>
+        <v>5.69283580780029</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>6.6560001373291</v>
       </c>
       <c r="G1021" t="n">
-        <v>5.63861751556396</v>
+        <v>5.63861799240112</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G1022" t="n">
-        <v>5.61405038833618</v>
+        <v>5.61404991149902</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G1023" t="n">
-        <v>5.59964942932129</v>
+        <v>5.59964990615845</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>6.58400011062622</v>
       </c>
       <c r="G1024" t="n">
-        <v>5.57762336730957</v>
+        <v>5.57762384414673</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>6.57800006866455</v>
       </c>
       <c r="G1025" t="n">
-        <v>5.57254076004028</v>
+        <v>5.57254028320312</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>6.65500020980835</v>
       </c>
       <c r="G1027" t="n">
-        <v>5.63777112960815</v>
+        <v>5.63777160644531</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1029" t="n">
-        <v>5.4048056602478</v>
+        <v>5.40480470657349</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G1030" t="n">
-        <v>5.45478630065918</v>
+        <v>5.45478773117065</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>6.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>5.50646305084229</v>
+        <v>5.50646257400513</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G1032" t="n">
-        <v>5.59964942932129</v>
+        <v>5.59964990615845</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>6.5</v>
       </c>
       <c r="G1034" t="n">
-        <v>5.50646305084229</v>
+        <v>5.50646257400513</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1035" t="n">
-        <v>5.46410512924194</v>
+        <v>5.4641056060791</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>6.45300006866455</v>
       </c>
       <c r="G1038" t="n">
-        <v>5.46664714813232</v>
+        <v>5.46664667129517</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>6.61600017547607</v>
       </c>
       <c r="G1040" t="n">
-        <v>5.60473203659058</v>
+        <v>5.60473155975342</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>6.48799991607666</v>
       </c>
       <c r="G1041" t="n">
-        <v>5.49629735946655</v>
+        <v>5.49629783630371</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>6.47900009155273</v>
       </c>
       <c r="G1042" t="n">
-        <v>5.48867225646973</v>
+        <v>5.48867273330688</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.53611326217651</v>
+        <v>5.53611278533936</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1045" t="n">
-        <v>5.60811996459961</v>
+        <v>5.60812091827393</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1046" t="n">
-        <v>5.63353586196899</v>
+        <v>5.63353538513184</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>6.74900007247925</v>
       </c>
       <c r="G1047" t="n">
-        <v>5.71740245819092</v>
+        <v>5.71740341186523</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1049" t="n">
-        <v>5.80296421051025</v>
+        <v>5.80296468734741</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>5.22690391540527</v>
+        <v>5.22690343856812</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>6.19600009918213</v>
       </c>
       <c r="G1055" t="n">
-        <v>5.24892997741699</v>
+        <v>5.24892950057983</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>6.00299978256226</v>
       </c>
       <c r="G1056" t="n">
-        <v>5.08542966842651</v>
+        <v>5.08543014526367</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>4.90498781204224</v>
+        <v>4.90498828887939</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>5.98600006103516</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.07102918624878</v>
+        <v>5.07102870941162</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.90350008010864</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.15399074554443</v>
+        <v>4.15399026870728</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.97700023651123</v>
       </c>
       <c r="G1065" t="n">
-        <v>4.2162561416626</v>
+        <v>4.21625709533691</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.89688205718994</v>
+        <v>3.89688158035278</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>4.36149978637695</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.69483685493469</v>
+        <v>3.69483613967896</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>4.5</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.81216645240784</v>
+        <v>3.81216669082642</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G1072" t="n">
-        <v>4.08748960494995</v>
+        <v>4.08749008178711</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>4.41849994659424</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.74312376976013</v>
+        <v>3.74312400817871</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>4.70300006866455</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.98413801193237</v>
+        <v>3.98413753509521</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>4.6875</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.97100710868835</v>
+        <v>3.9710066318512</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>4.27809810638428</v>
+        <v>4.27809858322144</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>5</v>
       </c>
       <c r="G1083" t="n">
-        <v>4.23574113845825</v>
+        <v>4.23574066162109</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1085" t="n">
-        <v>4.51529979705811</v>
+        <v>4.51529932022095</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1087" t="n">
-        <v>4.53224229812622</v>
+        <v>4.53224182128906</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1089" t="n">
-        <v>4.27809810638428</v>
+        <v>4.27809858322144</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1090" t="n">
-        <v>4.47294187545776</v>
+        <v>4.47294282913208</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.43058490753174</v>
+        <v>4.43058443069458</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1099" t="n">
-        <v>4.7355580329895</v>
+        <v>4.73555898666382</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1105" t="n">
-        <v>4.52377128601074</v>
+        <v>4.52377080917358</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1110" t="n">
-        <v>4.80596113204956</v>
+        <v>4.8059606552124</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.7016716003418</v>
+        <v>4.70167207717896</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1112" t="n">
-        <v>4.63214683532715</v>
+        <v>4.63214635848999</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1114" t="n">
-        <v>4.81465148925781</v>
+        <v>4.81465101242065</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>5.75</v>
       </c>
       <c r="G1115" t="n">
-        <v>4.99715662002563</v>
+        <v>4.99715614318848</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.11013507843018</v>
+        <v>5.11013555526733</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1117" t="n">
-        <v>5.0840630531311</v>
+        <v>5.08406352996826</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.18835163116455</v>
+        <v>5.18835115432739</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.37954807281494</v>
+        <v>5.37954711914062</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1123" t="n">
-        <v>5.48383665084839</v>
+        <v>5.48383617401123</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1128" t="n">
-        <v>5.19704294204712</v>
+        <v>5.19704246520996</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1131" t="n">
-        <v>5.48383665084839</v>
+        <v>5.48383617401123</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.49252653121948</v>
+        <v>5.49252700805664</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1136" t="n">
-        <v>5.56205224990845</v>
+        <v>5.56205177307129</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.50121688842773</v>
+        <v>5.50121736526489</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.50121688842773</v>
+        <v>5.50121736526489</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1141" t="n">
-        <v>5.50121688842773</v>
+        <v>5.50121736526489</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1143" t="n">
-        <v>5.59681558609009</v>
+        <v>5.59681510925293</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1144" t="n">
-        <v>5.56205224990845</v>
+        <v>5.56205177307129</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.44907331466675</v>
+        <v>5.44907283782959</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1148" t="n">
-        <v>5.19704294204712</v>
+        <v>5.19704246520996</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.41431045532227</v>
+        <v>5.41430997848511</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1150" t="n">
-        <v>5.34478521347046</v>
+        <v>5.3447847366333</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.34478521347046</v>
+        <v>5.3447847366333</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1153" t="n">
-        <v>5.41431045532227</v>
+        <v>5.41430997848511</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1155" t="n">
-        <v>5.30133008956909</v>
+        <v>5.30133104324341</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>5.75</v>
       </c>
       <c r="G1160" t="n">
-        <v>4.99715662002563</v>
+        <v>4.99715614318848</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1164" t="n">
-        <v>5.0840630531311</v>
+        <v>5.08406352996826</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1167" t="n">
-        <v>5.25787782669067</v>
+        <v>5.25787734985352</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1171" t="n">
-        <v>5.47514486312866</v>
+        <v>5.4751443862915</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>5.50121688842773</v>
+        <v>5.50121736526489</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1175" t="n">
-        <v>5.47514486312866</v>
+        <v>5.4751443862915</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1177" t="n">
-        <v>5.44907331466675</v>
+        <v>5.44907283782959</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1180" t="n">
-        <v>5.38823843002319</v>
+        <v>5.38823747634888</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1183" t="n">
-        <v>5.26656723022461</v>
+        <v>5.26656818389893</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1185" t="n">
-        <v>5.0840630531311</v>
+        <v>5.08406352996826</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1187" t="n">
-        <v>5.23180484771729</v>
+        <v>5.23180532455444</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1191" t="n">
-        <v>5.09275436401367</v>
+        <v>5.09275388717651</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>6</v>
       </c>
       <c r="G1193" t="n">
-        <v>5.21442365646362</v>
+        <v>5.21442413330078</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>6</v>
       </c>
       <c r="G1200" t="n">
-        <v>5.21442365646362</v>
+        <v>5.21442413330078</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1202" t="n">
-        <v>5.25787782669067</v>
+        <v>5.25787734985352</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>6</v>
       </c>
       <c r="G1203" t="n">
-        <v>5.21442365646362</v>
+        <v>5.21442413330078</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1208" t="n">
-        <v>5.04929971694946</v>
+        <v>5.04930019378662</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>5.75</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.99715662002563</v>
+        <v>4.99715614318848</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.09275436401367</v>
+        <v>5.09275388717651</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1216" t="n">
-        <v>5.23180484771729</v>
+        <v>5.23180532455444</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1219" t="n">
-        <v>5.18835163116455</v>
+        <v>5.18835115432739</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1220" t="n">
-        <v>5.0840630531311</v>
+        <v>5.08406352996826</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.91894006729126</v>
+        <v>4.9189395904541</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1228" t="n">
-        <v>4.62345552444458</v>
+        <v>4.62345600128174</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1230" t="n">
-        <v>4.89286756515503</v>
+        <v>4.89286804199219</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1233" t="n">
-        <v>4.78857946395874</v>
+        <v>4.78857898712158</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>6.75</v>
       </c>
       <c r="G1239" t="n">
-        <v>5.86622667312622</v>
+        <v>5.86622714996338</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1241" t="n">
-        <v>5.97920608520508</v>
+        <v>5.97920656204224</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1243" t="n">
-        <v>6.05742216110229</v>
+        <v>6.05742263793945</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1245" t="n">
-        <v>6.15301990509033</v>
+        <v>6.15302038192749</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1249" t="n">
-        <v>6.17909240722656</v>
+        <v>6.17909288406372</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1250" t="n">
-        <v>5.98789691925049</v>
+        <v>5.98789644241333</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.92706155776978</v>
+        <v>5.92706203460693</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>6.75</v>
       </c>
       <c r="G1257" t="n">
-        <v>5.86622667312622</v>
+        <v>5.86622714996338</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>6.75</v>
       </c>
       <c r="G1260" t="n">
-        <v>5.86622667312622</v>
+        <v>5.86622714996338</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.81408214569092</v>
+        <v>5.81408262252808</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.82277297973633</v>
+        <v>5.82277345657349</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1264" t="n">
-        <v>5.79670143127441</v>
+        <v>5.79670190811157</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1265" t="n">
-        <v>5.82277297973633</v>
+        <v>5.82277345657349</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1266" t="n">
-        <v>5.79670143127441</v>
+        <v>5.79670190811157</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1267" t="n">
-        <v>5.78801012039185</v>
+        <v>5.788010597229</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1268" t="n">
-        <v>5.79670143127441</v>
+        <v>5.79670190811157</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1269" t="n">
-        <v>5.81408214569092</v>
+        <v>5.81408262252808</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1271" t="n">
-        <v>5.78801012039185</v>
+        <v>5.788010597229</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.79670143127441</v>
+        <v>5.79670190811157</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.81408214569092</v>
+        <v>5.81408262252808</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1275" t="n">
-        <v>6.10087585449219</v>
+        <v>6.10087537765503</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1278" t="n">
-        <v>6.3268346786499</v>
+        <v>6.32683372497559</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1280" t="n">
-        <v>6.10087585449219</v>
+        <v>6.10087537765503</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1282" t="n">
-        <v>6.14433002471924</v>
+        <v>6.1443305015564</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1284" t="n">
-        <v>6.07480335235596</v>
+        <v>6.07480382919312</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1286" t="n">
-        <v>5.79670143127441</v>
+        <v>5.79670190811157</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1288" t="n">
-        <v>5.99658727645874</v>
+        <v>5.9965877532959</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>7</v>
       </c>
       <c r="G1289" t="n">
-        <v>6.08349418640137</v>
+        <v>6.08349466323853</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1291" t="n">
-        <v>6.04873132705688</v>
+        <v>6.04873180389404</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1292" t="n">
-        <v>6.13563919067383</v>
+        <v>6.13563871383667</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1296" t="n">
-        <v>7.28281164169312</v>
+        <v>7.28281211853027</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1299" t="n">
-        <v>7.47400808334351</v>
+        <v>7.47400760650635</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1300" t="n">
-        <v>7.47400808334351</v>
+        <v>7.47400760650635</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1301" t="n">
-        <v>7.52615213394165</v>
+        <v>7.52615165710449</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1302" t="n">
-        <v>7.3697190284729</v>
+        <v>7.36971855163574</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1303" t="n">
-        <v>7.16114282608032</v>
+        <v>7.16114234924316</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1304" t="n">
-        <v>7.1524510383606</v>
+        <v>7.15245056152344</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1305" t="n">
-        <v>7.1524510383606</v>
+        <v>7.15245056152344</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1306" t="n">
-        <v>7.16114282608032</v>
+        <v>7.16114234924316</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1307" t="n">
-        <v>7.03078126907349</v>
+        <v>7.03078174591064</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1309" t="n">
-        <v>6.98732757568359</v>
+        <v>6.98732805252075</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1311" t="n">
-        <v>7.28281164169312</v>
+        <v>7.28281211853027</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.0394721031189</v>
+        <v>7.03947257995605</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1318" t="n">
-        <v>7.28281164169312</v>
+        <v>7.28281211853027</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1321" t="n">
-        <v>7.49138879776001</v>
+        <v>7.49138927459717</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>7.35233736038208</v>
+        <v>7.35233688354492</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1325" t="n">
-        <v>7.30019378662109</v>
+        <v>7.30019330978394</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1326" t="n">
-        <v>7.1524510383606</v>
+        <v>7.15245056152344</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1327" t="n">
-        <v>7.02209091186523</v>
+        <v>7.02209138870239</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1328" t="n">
-        <v>7.30019378662109</v>
+        <v>7.30019330978394</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1329" t="n">
-        <v>7.47400808334351</v>
+        <v>7.47400760650635</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1330" t="n">
-        <v>7.45662641525269</v>
+        <v>7.45662689208984</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1331" t="n">
-        <v>7.51746082305908</v>
+        <v>7.51746034622192</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1332" t="n">
-        <v>7.52615213394165</v>
+        <v>7.52615165710449</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1335" t="n">
-        <v>8.02152156829834</v>
+        <v>8.02152061462402</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1336" t="n">
-        <v>7.92592525482178</v>
+        <v>7.92592477798462</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1339" t="n">
-        <v>8.03021240234375</v>
+        <v>8.03021335601807</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>9</v>
       </c>
       <c r="G1340" t="n">
-        <v>7.8216347694397</v>
+        <v>7.82163524627686</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G1342" t="n">
-        <v>7.91723394393921</v>
+        <v>7.91723346710205</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1344" t="n">
-        <v>7.87378025054932</v>
+        <v>7.87378072738647</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1345" t="n">
-        <v>7.83901739120483</v>
+        <v>7.83901786804199</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1346" t="n">
-        <v>7.92592525482178</v>
+        <v>7.92592477798462</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1347" t="n">
-        <v>7.90854263305664</v>
+        <v>7.9085431098938</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1348" t="n">
-        <v>7.90854263305664</v>
+        <v>7.9085431098938</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G1349" t="n">
-        <v>7.9693775177002</v>
+        <v>7.96937847137451</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1351" t="n">
-        <v>7.97806835174561</v>
+        <v>7.97806882858276</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1353" t="n">
-        <v>8.06497573852539</v>
+        <v>8.06497669219971</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1354" t="n">
-        <v>8.26486206054688</v>
+        <v>8.26486301422119</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>9.5</v>
       </c>
       <c r="G1357" t="n">
-        <v>8.25617122650146</v>
+        <v>8.25617027282715</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1358" t="n">
-        <v>8.26486206054688</v>
+        <v>8.26486301422119</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1359" t="n">
-        <v>8.46474647521973</v>
+        <v>8.46474742889404</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1360" t="n">
-        <v>8.24747943878174</v>
+        <v>8.24748039245605</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1361" t="n">
-        <v>8.24747943878174</v>
+        <v>8.24748039245605</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1362" t="n">
-        <v>8.24747943878174</v>
+        <v>8.24748039245605</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1363" t="n">
-        <v>8.26486206054688</v>
+        <v>8.26486301422119</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1364" t="n">
-        <v>8.29132270812988</v>
+        <v>8.29132175445557</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G1366" t="n">
-        <v>8.25604057312012</v>
+        <v>8.25604152679443</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>9.5</v>
       </c>
       <c r="G1369" t="n">
-        <v>8.37952899932861</v>
+        <v>8.3795280456543</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G1372" t="n">
-        <v>8.25604057312012</v>
+        <v>8.25604152679443</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1374" t="n">
-        <v>8.29132270812988</v>
+        <v>8.29132175445557</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1375" t="n">
-        <v>8.4412727355957</v>
+        <v>8.44127368927002</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1379" t="n">
-        <v>8.55594062805176</v>
+        <v>8.55593872070312</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1380" t="n">
-        <v>8.50301647186279</v>
+        <v>8.50301742553711</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1382" t="n">
-        <v>8.32660484313965</v>
+        <v>8.32660579681396</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G1384" t="n">
-        <v>8.35306644439697</v>
+        <v>8.35306739807129</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G1385" t="n">
-        <v>8.28250312805176</v>
+        <v>8.28250217437744</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1389" t="n">
-        <v>7.98260354995728</v>
+        <v>7.98260498046875</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G1390" t="n">
-        <v>7.91203880310059</v>
+        <v>7.91203927993774</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1391" t="n">
-        <v>7.87675857543945</v>
+        <v>7.87675762176514</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1392" t="n">
-        <v>7.8855767250061</v>
+        <v>7.88557720184326</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1393" t="n">
-        <v>7.98260354995728</v>
+        <v>7.98260498046875</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>7.78855037689209</v>
+        <v>7.78855085372925</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1395" t="n">
-        <v>7.83265590667725</v>
+        <v>7.83265495300293</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1396" t="n">
-        <v>7.58567953109741</v>
+        <v>7.58567905426025</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1397" t="n">
-        <v>7.69152641296387</v>
+        <v>7.69152545928955</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1400" t="n">
-        <v>7.57685804367065</v>
+        <v>7.57685852050781</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1403" t="n">
-        <v>8.00024509429932</v>
+        <v>8.000244140625</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1405" t="n">
-        <v>7.99142408370972</v>
+        <v>7.99142503738403</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1407" t="n">
-        <v>8.04434871673584</v>
+        <v>8.04434776306152</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1408" t="n">
-        <v>7.79737138748169</v>
+        <v>7.79737234115601</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1413" t="n">
-        <v>8.00024509429932</v>
+        <v>8.000244140625</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1414" t="n">
-        <v>8.07080841064453</v>
+        <v>8.07080936431885</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1415" t="n">
-        <v>7.95614242553711</v>
+        <v>7.95614290237427</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1416" t="n">
-        <v>7.95614242553711</v>
+        <v>7.95614290237427</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>9.5</v>
       </c>
       <c r="G1418" t="n">
-        <v>8.37952899932861</v>
+        <v>8.3795280456543</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G1419" t="n">
-        <v>8.28250312805176</v>
+        <v>8.28250217437744</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G1421" t="n">
-        <v>8.21193981170654</v>
+        <v>8.21193885803223</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G1422" t="n">
-        <v>8.17665576934814</v>
+        <v>8.17665672302246</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>9.25</v>
       </c>
       <c r="G1423" t="n">
-        <v>8.15901470184326</v>
+        <v>8.15901565551758</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>9.25</v>
       </c>
       <c r="G1424" t="n">
-        <v>8.15901470184326</v>
+        <v>8.15901565551758</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1426" t="n">
-        <v>8.50301647186279</v>
+        <v>8.50301742553711</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1428" t="n">
-        <v>8.45009231567383</v>
+        <v>8.45009326934814</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G1431" t="n">
-        <v>8.21193981170654</v>
+        <v>8.21193885803223</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1434" t="n">
-        <v>8.13255310058594</v>
+        <v>8.13255405426025</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1437" t="n">
-        <v>8.45009231567383</v>
+        <v>8.45009326934814</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1439" t="n">
-        <v>8.59122180938721</v>
+        <v>8.59122276306152</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1442" t="n">
-        <v>8.37070846557617</v>
+        <v>8.37070751190186</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G1443" t="n">
-        <v>8.31778430938721</v>
+        <v>8.31778621673584</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1444" t="n">
-        <v>8.29132270812988</v>
+        <v>8.29132175445557</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G1445" t="n">
-        <v>8.31778430938721</v>
+        <v>8.31778621673584</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1446" t="n">
-        <v>8.07962989807129</v>
+        <v>8.07963085174561</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G1447" t="n">
-        <v>8.21193981170654</v>
+        <v>8.21193885803223</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1448" t="n">
-        <v>8.04434871673584</v>
+        <v>8.04434776306152</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1449" t="n">
-        <v>8.02670764923096</v>
+        <v>8.02670669555664</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.98260354995728</v>
+        <v>7.98260498046875</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1456" t="n">
-        <v>7.81501293182373</v>
+        <v>7.81501197814941</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1457" t="n">
-        <v>7.85029602050781</v>
+        <v>7.85029554367065</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1458" t="n">
-        <v>7.69152641296387</v>
+        <v>7.69152545928955</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>8.75</v>
       </c>
       <c r="G1459" t="n">
-        <v>7.71798658370972</v>
+        <v>7.71798706054688</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>8.5</v>
       </c>
       <c r="G1464" t="n">
-        <v>7.497474193573</v>
+        <v>7.49747371673584</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1472" t="n">
-        <v>8.05316829681396</v>
+        <v>8.05316734313965</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1474" t="n">
-        <v>8.01788711547852</v>
+        <v>8.0178861618042</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1475" t="n">
-        <v>8.04434871673584</v>
+        <v>8.04434776306152</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1476" t="n">
-        <v>7.98260354995728</v>
+        <v>7.98260498046875</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1477" t="n">
-        <v>8.01788711547852</v>
+        <v>8.0178861618042</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1478" t="n">
-        <v>8.05316829681396</v>
+        <v>8.05316734313965</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1479" t="n">
-        <v>8.00024509429932</v>
+        <v>8.000244140625</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1482" t="n">
-        <v>8.02670764923096</v>
+        <v>8.02670669555664</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1483" t="n">
-        <v>8.01788711547852</v>
+        <v>8.0178861618042</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1484" t="n">
-        <v>8.07080841064453</v>
+        <v>8.07080936431885</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1485" t="n">
-        <v>8.02670764923096</v>
+        <v>8.02670669555664</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1486" t="n">
-        <v>7.98260354995728</v>
+        <v>7.98260498046875</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1487" t="n">
-        <v>8.07080841064453</v>
+        <v>8.07080936431885</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1488" t="n">
-        <v>8.01788711547852</v>
+        <v>8.0178861618042</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1491" t="n">
-        <v>8.07080841064453</v>
+        <v>8.07080936431885</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1494" t="n">
-        <v>7.83265590667725</v>
+        <v>7.83265495300293</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1496" t="n">
-        <v>7.83265590667725</v>
+        <v>7.83265495300293</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1501" t="n">
-        <v>7.45337009429932</v>
+        <v>7.45337057113647</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1506" t="n">
-        <v>7.30342102050781</v>
+        <v>7.30342054367065</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1508" t="n">
-        <v>7.19757413864136</v>
+        <v>7.19757461547852</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1509" t="n">
-        <v>7.28577995300293</v>
+        <v>7.28578042984009</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1511" t="n">
-        <v>7.31224203109741</v>
+        <v>7.31224155426025</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1513" t="n">
-        <v>7.19757413864136</v>
+        <v>7.19757461547852</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1516" t="n">
-        <v>7.15347146987915</v>
+        <v>7.15347194671631</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1517" t="n">
-        <v>7.14465141296387</v>
+        <v>7.14465093612671</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1519" t="n">
-        <v>7.10936880111694</v>
+        <v>7.1093692779541</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1521" t="n">
-        <v>7.19757413864136</v>
+        <v>7.19757461547852</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1522" t="n">
-        <v>7.38280630111694</v>
+        <v>7.3828067779541</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1525" t="n">
-        <v>7.47983121871948</v>
+        <v>7.47983169555664</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1531" t="n">
-        <v>7.31224203109741</v>
+        <v>7.31224155426025</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1532" t="n">
-        <v>7.30342102050781</v>
+        <v>7.30342054367065</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1540" t="n">
-        <v>7.29460000991821</v>
+        <v>7.29460048675537</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G1548" t="n">
-        <v>6.97706031799316</v>
+        <v>6.97705984115601</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1549" t="n">
-        <v>7.14465141296387</v>
+        <v>7.14465093612671</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1552" t="n">
-        <v>6.73890495300293</v>
+        <v>6.73890542984009</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1555" t="n">
-        <v>7.14465141296387</v>
+        <v>7.14465093612671</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1558" t="n">
-        <v>6.99470090866089</v>
+        <v>6.99470138549805</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1559" t="n">
-        <v>7.04762506484985</v>
+        <v>7.0476245880127</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1560" t="n">
-        <v>6.85357236862183</v>
+        <v>6.85357284545898</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1561" t="n">
-        <v>6.92413663864136</v>
+        <v>6.92413711547852</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1562" t="n">
-        <v>6.65952014923096</v>
+        <v>6.65952062606812</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1564" t="n">
-        <v>6.52721214294434</v>
+        <v>6.52721261978149</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1566" t="n">
-        <v>6.4566478729248</v>
+        <v>6.45664739608765</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>6.5</v>
       </c>
       <c r="G1571" t="n">
-        <v>5.73336172103882</v>
+        <v>5.73336124420166</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1572" t="n">
-        <v>5.71572065353394</v>
+        <v>5.71572113037109</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1575" t="n">
-        <v>5.96269655227661</v>
+        <v>5.96269607543945</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1576" t="n">
-        <v>6.0156192779541</v>
+        <v>6.01561975479126</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1577" t="n">
-        <v>6.21849298477173</v>
+        <v>6.21849203109741</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1578" t="n">
-        <v>6.10382509231567</v>
+        <v>6.10382556915283</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1579" t="n">
-        <v>6.33315944671631</v>
+        <v>6.33315896987915</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1582" t="n">
-        <v>6.15674877166748</v>
+        <v>6.15674829483032</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G1583" t="n">
-        <v>6.1832103729248</v>
+        <v>6.18321084976196</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1585" t="n">
-        <v>5.90095186233521</v>
+        <v>5.90095233917236</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1587" t="n">
-        <v>5.99797868728638</v>
+        <v>5.99797916412354</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1588" t="n">
-        <v>6.13910722732544</v>
+        <v>6.1391077041626</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1591" t="n">
-        <v>6.16556882858276</v>
+        <v>6.16556930541992</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1595" t="n">
-        <v>5.74218273162842</v>
+        <v>5.74218320846558</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1596" t="n">
-        <v>5.79510641098022</v>
+        <v>5.79510593414307</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1597" t="n">
-        <v>5.76864385604858</v>
+        <v>5.76864433288574</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1598" t="n">
-        <v>5.81274700164795</v>
+        <v>5.81274747848511</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1606" t="n">
-        <v>5.85685014724731</v>
+        <v>5.85684967041016</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1607" t="n">
-        <v>5.79510641098022</v>
+        <v>5.79510593414307</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1609" t="n">
-        <v>5.85685014724731</v>
+        <v>5.85684967041016</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1614" t="n">
-        <v>5.84802961349487</v>
+        <v>5.84802913665771</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1616" t="n">
-        <v>5.74218273162842</v>
+        <v>5.74218320846558</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1617" t="n">
-        <v>5.84802961349487</v>
+        <v>5.84802913665771</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1619" t="n">
-        <v>5.99797868728638</v>
+        <v>5.99797916412354</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1624" t="n">
-        <v>5.81274700164795</v>
+        <v>5.81274747848511</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G1626" t="n">
-        <v>5.82181549072266</v>
+        <v>5.8218150138855</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1627" t="n">
-        <v>5.83995199203491</v>
+        <v>5.83995246887207</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1629" t="n">
-        <v>6.1482720375061</v>
+        <v>6.14827251434326</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1636" t="n">
-        <v>6.10293054580688</v>
+        <v>6.10293102264404</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1641" t="n">
-        <v>5.71299600601196</v>
+        <v>5.71299648284912</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1642" t="n">
-        <v>5.80367851257324</v>
+        <v>5.8036789894104</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1643" t="n">
-        <v>5.76740598678589</v>
+        <v>5.76740550994873</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1645" t="n">
-        <v>5.88529300689697</v>
+        <v>5.88529253005981</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G1646" t="n">
-        <v>5.82181549072266</v>
+        <v>5.8218150138855</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1648" t="n">
-        <v>5.80367851257324</v>
+        <v>5.8036789894104</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1655" t="n">
-        <v>5.60417699813843</v>
+        <v>5.60417747497559</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1657" t="n">
-        <v>5.33212995529175</v>
+        <v>5.33212947845459</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1662" t="n">
-        <v>5.60417699813843</v>
+        <v>5.60417747497559</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1668" t="n">
-        <v>5.60417699813843</v>
+        <v>5.60417747497559</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1673" t="n">
-        <v>5.54069995880127</v>
+        <v>5.54070043563843</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1675" t="n">
-        <v>5.60417699813843</v>
+        <v>5.60417747497559</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1678" t="n">
-        <v>5.71299600601196</v>
+        <v>5.71299648284912</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1682" t="n">
-        <v>5.90342998504639</v>
+        <v>5.90343046188354</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1683" t="n">
-        <v>5.90342998504639</v>
+        <v>5.90343046188354</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1695" t="n">
-        <v>5.27772045135498</v>
+        <v>5.27772092819214</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1701" t="n">
-        <v>5.10542345046997</v>
+        <v>5.10542392730713</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1702" t="n">
-        <v>5.08728694915771</v>
+        <v>5.08728742599487</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1704" t="n">
-        <v>5.26865196228027</v>
+        <v>5.26865148544312</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1706" t="n">
-        <v>5.02380895614624</v>
+        <v>5.0238094329834</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1707" t="n">
-        <v>5.08728694915771</v>
+        <v>5.08728742599487</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1715" t="n">
-        <v>4.90592193603516</v>
+        <v>4.90592241287231</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1718" t="n">
-        <v>5.06915092468262</v>
+        <v>5.06915044784546</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1723" t="n">
-        <v>4.89685440063477</v>
+        <v>4.89685392379761</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1728" t="n">
-        <v>4.8696494102478</v>
+        <v>4.86964893341064</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1733" t="n">
-        <v>5.06915092468262</v>
+        <v>5.06915044784546</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1735" t="n">
-        <v>5.22331094741821</v>
+        <v>5.22331142425537</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G1739" t="n">
-        <v>5.3411979675293</v>
+        <v>5.34119844436646</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1740" t="n">
-        <v>5.40467596054077</v>
+        <v>5.40467643737793</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1743" t="n">
-        <v>5.45001745223999</v>
+        <v>5.45001697540283</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1753" t="n">
-        <v>5.80367851257324</v>
+        <v>5.8036789894104</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1754" t="n">
-        <v>5.77647352218628</v>
+        <v>5.77647399902344</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1756" t="n">
-        <v>5.76740598678589</v>
+        <v>5.76740550994873</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1758" t="n">
-        <v>5.79461097717285</v>
+        <v>5.79461050033569</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1763" t="n">
-        <v>5.62231397628784</v>
+        <v>5.62231349945068</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1766" t="n">
-        <v>5.45001745223999</v>
+        <v>5.45001697540283</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1769" t="n">
-        <v>5.54069995880127</v>
+        <v>5.54070043563843</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1771" t="n">
-        <v>5.62231397628784</v>
+        <v>5.62231349945068</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G1775" t="n">
-        <v>5.52256345748901</v>
+        <v>5.52256298065186</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G1778" t="n">
-        <v>5.52256345748901</v>
+        <v>5.52256298065186</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1779" t="n">
-        <v>5.62231397628784</v>
+        <v>5.62231349945068</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1783" t="n">
-        <v>5.62231397628784</v>
+        <v>5.62231349945068</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1785" t="n">
-        <v>5.62231397628784</v>
+        <v>5.62231349945068</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1786" t="n">
-        <v>5.62231397628784</v>
+        <v>5.62231349945068</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1788" t="n">
-        <v>5.75833797454834</v>
+        <v>5.75833749771118</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1791" t="n">
-        <v>5.76740598678589</v>
+        <v>5.76740550994873</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1793" t="n">
-        <v>5.80367851257324</v>
+        <v>5.8036789894104</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1796" t="n">
-        <v>5.83995199203491</v>
+        <v>5.83995246887207</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1798" t="n">
-        <v>5.83995199203491</v>
+        <v>5.83995246887207</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1799" t="n">
-        <v>5.80367851257324</v>
+        <v>5.8036789894104</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G1800" t="n">
-        <v>5.82181549072266</v>
+        <v>5.8218150138855</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1804" t="n">
-        <v>6.56541156768799</v>
+        <v>6.56541109085083</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1807" t="n">
-        <v>6.64702558517456</v>
+        <v>6.64702606201172</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1810" t="n">
-        <v>7.08230113983154</v>
+        <v>7.0823016166687</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1815" t="n">
-        <v>7.32714462280273</v>
+        <v>7.32714414596558</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G1816" t="n">
-        <v>7.27273511886597</v>
+        <v>7.27273559570312</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1818" t="n">
-        <v>7.3996901512146</v>
+        <v>7.39969062805176</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1822" t="n">
-        <v>7.38155460357666</v>
+        <v>7.3815541267395</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1828" t="n">
-        <v>7.41782712936401</v>
+        <v>7.41782760620117</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1829" t="n">
-        <v>7.3996901512146</v>
+        <v>7.39969062805176</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1837" t="n">
-        <v>7.08230113983154</v>
+        <v>7.0823016166687</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1838" t="n">
-        <v>7.08230113983154</v>
+        <v>7.0823016166687</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1839" t="n">
-        <v>7.26366710662842</v>
+        <v>7.26366662979126</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1842" t="n">
-        <v>7.00975608825684</v>
+        <v>7.00975561141968</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1849" t="n">
-        <v>7.14578008651733</v>
+        <v>7.14577960968018</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1851" t="n">
-        <v>7.0641655921936</v>
+        <v>7.06416511535645</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1862" t="n">
-        <v>6.90093660354614</v>
+        <v>6.9009370803833</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1865" t="n">
-        <v>6.90093660354614</v>
+        <v>6.9009370803833</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1869" t="n">
-        <v>7.14578008651733</v>
+        <v>7.14577960968018</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1873" t="n">
-        <v>7.14578008651733</v>
+        <v>7.14577960968018</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1874" t="n">
-        <v>7.04602813720703</v>
+        <v>7.04602861404419</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1878" t="n">
-        <v>6.90093660354614</v>
+        <v>6.9009370803833</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1883" t="n">
-        <v>6.7139105796814</v>
+        <v>6.71391105651855</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1885" t="n">
-        <v>6.72324800491333</v>
+        <v>6.72324848175049</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1888" t="n">
-        <v>6.70457220077515</v>
+        <v>6.7045726776123</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1889" t="n">
-        <v>6.84463977813721</v>
+        <v>6.84464025497437</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G1891" t="n">
-        <v>6.73258590698242</v>
+        <v>6.73258638381958</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1892" t="n">
-        <v>6.7139105796814</v>
+        <v>6.71391105651855</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1893" t="n">
-        <v>6.83530235290527</v>
+        <v>6.83530282974243</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1898" t="n">
-        <v>6.82596445083618</v>
+        <v>6.82596492767334</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1908" t="n">
-        <v>6.83530235290527</v>
+        <v>6.83530282974243</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1910" t="n">
-        <v>7.0127215385437</v>
+        <v>7.01272201538086</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1912" t="n">
-        <v>6.72324800491333</v>
+        <v>6.72324848175049</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1914" t="n">
-        <v>6.7139105796814</v>
+        <v>6.71391105651855</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1915" t="n">
-        <v>6.58318090438843</v>
+        <v>6.58318042755127</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1916" t="n">
-        <v>6.7139105796814</v>
+        <v>6.71391105651855</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1922" t="n">
-        <v>7.15278911590576</v>
+        <v>7.1527886390686</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1924" t="n">
-        <v>7.4142484664917</v>
+        <v>7.41424894332886</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1928" t="n">
-        <v>7.76908683776855</v>
+        <v>7.76908731460571</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1932" t="n">
-        <v>7.89047956466675</v>
+        <v>7.89047861099243</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1933" t="n">
-        <v>7.90915536880493</v>
+        <v>7.90915441513062</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1937" t="n">
-        <v>7.80643749237061</v>
+        <v>7.80643796920776</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1938" t="n">
-        <v>7.86246585845947</v>
+        <v>7.86246538162231</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1939" t="n">
-        <v>7.7410740852356</v>
+        <v>7.74107360839844</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1940" t="n">
-        <v>7.80643749237061</v>
+        <v>7.80643796920776</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1951" t="n">
-        <v>7.61034297943115</v>
+        <v>7.61034345626831</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1954" t="n">
-        <v>7.61034297943115</v>
+        <v>7.61034345626831</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1955" t="n">
-        <v>7.56365489959717</v>
+        <v>7.56365442276001</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1957" t="n">
-        <v>7.47961378097534</v>
+        <v>7.4796142578125</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1958" t="n">
-        <v>7.47961378097534</v>
+        <v>7.4796142578125</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1959" t="n">
-        <v>7.42358636856079</v>
+        <v>7.42358684539795</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1962" t="n">
-        <v>7.18080282211304</v>
+        <v>7.18080234527588</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1964" t="n">
-        <v>7.15278911590576</v>
+        <v>7.1527886390686</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1966" t="n">
-        <v>7.18080282211304</v>
+        <v>7.18080234527588</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1967" t="n">
-        <v>7.15278911590576</v>
+        <v>7.1527886390686</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1968" t="n">
-        <v>7.02205896377563</v>
+        <v>7.02205944061279</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1974" t="n">
-        <v>6.89132928848267</v>
+        <v>6.89132976531982</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1978" t="n">
-        <v>6.89132928848267</v>
+        <v>6.89132976531982</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1981" t="n">
-        <v>7.02205896377563</v>
+        <v>7.02205944061279</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1985" t="n">
-        <v>7.33020830154419</v>
+        <v>7.33020782470703</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1988" t="n">
-        <v>7.33020830154419</v>
+        <v>7.33020782470703</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1989" t="n">
-        <v>7.40491056442261</v>
+        <v>7.40491104125977</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1990" t="n">
-        <v>7.3675594329834</v>
+        <v>7.36755895614624</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1995" t="n">
-        <v>7.34888410568237</v>
+        <v>7.34888362884521</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52265,7 +52265,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1996" t="n">
-        <v>7.47961378097534</v>
+        <v>7.4796142578125</v>
       </c>
       <c r="H1996" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1999" t="n">
-        <v>7.80643749237061</v>
+        <v>7.80643796920776</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G2001" t="n">
-        <v>8.11458683013916</v>
+        <v>8.11458778381348</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2002" t="n">
-        <v>8.12392425537109</v>
+        <v>8.12392520904541</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>8.5</v>
       </c>
       <c r="G2003" t="n">
-        <v>7.93716812133789</v>
+        <v>7.93716859817505</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G2006" t="n">
-        <v>7.91849231719971</v>
+        <v>7.91849279403687</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>8.5</v>
       </c>
       <c r="G2007" t="n">
-        <v>7.93716812133789</v>
+        <v>7.93716859817505</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52603,7 +52603,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G2009" t="n">
-        <v>7.91849231719971</v>
+        <v>7.91849279403687</v>
       </c>
       <c r="H2009" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2020" t="n">
-        <v>8.12392425537109</v>
+        <v>8.12392520904541</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2033" t="n">
-        <v>9.00168323516846</v>
+        <v>9.00168228149414</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2039" t="n">
-        <v>8.68419647216797</v>
+        <v>8.68419551849365</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G2046" t="n">
-        <v>8.97366905212402</v>
+        <v>8.97366809844971</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G2048" t="n">
-        <v>8.88962936401367</v>
+        <v>8.88962841033936</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G2053" t="n">
-        <v>9.00168323516846</v>
+        <v>9.00168228149414</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G2055" t="n">
-        <v>9.30049324035645</v>
+        <v>9.30049419403076</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2059" t="n">
-        <v>9.16976261138916</v>
+        <v>9.16976356506348</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G2064" t="n">
-        <v>9.29115581512451</v>
+        <v>9.29115676879883</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G2066" t="n">
-        <v>8.51611423492432</v>
+        <v>8.51611518859863</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2075" t="n">
-        <v>8.68419647216797</v>
+        <v>8.68419551849365</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54501,7 +54501,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G2082" t="n">
-        <v>8.48810195922852</v>
+        <v>8.4881010055542</v>
       </c>
       <c r="H2082" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G2088" t="n">
-        <v>8.82426357269287</v>
+        <v>8.82426261901855</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2096" t="n">
-        <v>9.5432767868042</v>
+        <v>9.54327774047852</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G2097" t="n">
-        <v>9.58062839508057</v>
+        <v>9.58062934875488</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -54995,7 +54995,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G2101" t="n">
-        <v>9.56195259094238</v>
+        <v>9.5619535446167</v>
       </c>
       <c r="H2101" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G2103" t="n">
-        <v>9.5432767868042</v>
+        <v>9.54327774047852</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2107" t="n">
-        <v>9.4685754776001</v>
+        <v>9.46857452392578</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G2110" t="n">
-        <v>9.31916809082031</v>
+        <v>9.31916904449463</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55281,7 +55281,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G2112" t="n">
-        <v>9.16976261138916</v>
+        <v>9.16976356506348</v>
       </c>
       <c r="H2112" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G2113" t="n">
-        <v>9.05770969390869</v>
+        <v>9.05770874023438</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G2120" t="n">
-        <v>9.28181743621826</v>
+        <v>9.28181838989258</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55593,7 +55593,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G2124" t="n">
-        <v>9.69268226623535</v>
+        <v>9.69268321990967</v>
       </c>
       <c r="H2124" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2127" t="n">
-        <v>9.67400646209717</v>
+        <v>9.67400741577148</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>12.5299997329712</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>72929</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>12.5299997329712</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>12.5699996948242</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>12.8199996948242</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>12.8199996948242</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>
